--- a/public/downloads/mgfieldslanders2018.xlsx
+++ b/public/downloads/mgfieldslanders2018.xlsx
@@ -8,29 +8,31 @@
   </bookViews>
   <sheets>
     <sheet name="MLIP_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="anomaly" sheetId="2" r:id="rId2"/>
-    <sheet name="AlphaNet-v1-OMA" sheetId="3" r:id="rId3"/>
-    <sheet name="CHGNetv0.3.0" sheetId="4" r:id="rId4"/>
-    <sheet name="DPA-3.1-3M-FT" sheetId="5" r:id="rId5"/>
-    <sheet name="Eqnorm-MPtrj" sheetId="6" r:id="rId6"/>
-    <sheet name="eSEN-30M-OAM" sheetId="7" r:id="rId7"/>
-    <sheet name="GRACE-2L-OAM" sheetId="8" r:id="rId8"/>
-    <sheet name="MACE-MPA-0" sheetId="9" r:id="rId9"/>
-    <sheet name="MATLANTISv8" sheetId="10" r:id="rId10"/>
-    <sheet name="MatterSim_v1_5M" sheetId="11" r:id="rId11"/>
-    <sheet name="ORB-v3" sheetId="12" r:id="rId12"/>
-    <sheet name="SevenNet-MF-OMPA" sheetId="13" r:id="rId13"/>
-    <sheet name="UMA-m-1p1_oc20" sheetId="14" r:id="rId14"/>
-    <sheet name="UMA-m-1p1_omat" sheetId="15" r:id="rId15"/>
-    <sheet name="UMA-s-1p1_oc20" sheetId="16" r:id="rId16"/>
-    <sheet name="UMA-s-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
+    <sheet name="anomaly" sheetId="3" r:id="rId3"/>
+    <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
+    <sheet name="AlphaNet-v1-OMA" sheetId="5" r:id="rId5"/>
+    <sheet name="CHGNetv0.3.0" sheetId="6" r:id="rId6"/>
+    <sheet name="DPA-3.1-3M-FT" sheetId="7" r:id="rId7"/>
+    <sheet name="Eqnorm-MPtrj" sheetId="8" r:id="rId8"/>
+    <sheet name="eSEN-30M-OAM" sheetId="9" r:id="rId9"/>
+    <sheet name="GRACE-2L-OAM" sheetId="10" r:id="rId10"/>
+    <sheet name="MACE-MPA-0" sheetId="11" r:id="rId11"/>
+    <sheet name="MATLANTISv8" sheetId="12" r:id="rId12"/>
+    <sheet name="MatterSim_v1_5M" sheetId="13" r:id="rId13"/>
+    <sheet name="ORB-v3" sheetId="14" r:id="rId14"/>
+    <sheet name="SevenNet-MF-OMPA" sheetId="15" r:id="rId15"/>
+    <sheet name="UMA-m-1p1_oc20" sheetId="16" r:id="rId16"/>
+    <sheet name="UMA-m-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="UMA-s-1p1_oc20" sheetId="18" r:id="rId18"/>
+    <sheet name="UMA-s-1p1_omat" sheetId="19" r:id="rId19"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="57">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -62,10 +64,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
+    <t>Time_total (ms)</t>
   </si>
   <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -167,13 +169,34 @@
     <t>Adsorbate_name</t>
   </si>
   <si>
-    <t>OH</t>
+    <t>Gas shift correction</t>
+  </si>
+  <si>
+    <t>Shift (eV)</t>
+  </si>
+  <si>
+    <t>N_fit</t>
+  </si>
+  <si>
+    <t>MAE_total_shifted (eV)</t>
+  </si>
+  <si>
+    <t>MAE_normal_shifted (eV)</t>
+  </si>
+  <si>
+    <t>Num_normal_shifted</t>
+  </si>
+  <si>
+    <t>Num_energy_anomaly_shifted</t>
   </si>
   <si>
     <t>CHO</t>
   </si>
   <si>
     <t>CO</t>
+  </si>
+  <si>
+    <t>OH</t>
   </si>
   <si>
     <t>O</t>
@@ -665,10 +688,10 @@
         <v>35</v>
       </c>
       <c r="N3" s="5">
-        <v>1128.843299865723</v>
+        <v>1128843.299865723</v>
       </c>
       <c r="O3" s="4">
-        <v>0.03168327204989538</v>
+        <v>31.68327204989539</v>
       </c>
       <c r="P3" s="5">
         <v>35629</v>
@@ -715,10 +738,10 @@
         <v>35</v>
       </c>
       <c r="N4" s="5">
-        <v>269.7724313735962</v>
+        <v>269772.4313735962</v>
       </c>
       <c r="O4" s="4">
-        <v>0.04591089710238193</v>
+        <v>45.91089710238193</v>
       </c>
       <c r="P4" s="5">
         <v>5876</v>
@@ -765,10 +788,10 @@
         <v>35</v>
       </c>
       <c r="N5" s="5">
-        <v>1035.844679117203</v>
+        <v>1035844.679117203</v>
       </c>
       <c r="O5" s="4">
-        <v>0.1472206763952818</v>
+        <v>147.2206763952818</v>
       </c>
       <c r="P5" s="5">
         <v>7036</v>
@@ -815,10 +838,10 @@
         <v>35</v>
       </c>
       <c r="N6" s="5">
-        <v>469.9684545993805</v>
+        <v>469968.4545993805</v>
       </c>
       <c r="O6" s="4">
-        <v>0.08112695573957888</v>
+        <v>81.12695573957889</v>
       </c>
       <c r="P6" s="5">
         <v>5793</v>
@@ -865,10 +888,10 @@
         <v>35</v>
       </c>
       <c r="N7" s="5">
-        <v>3220.274775981903</v>
+        <v>3220274.775981903</v>
       </c>
       <c r="O7" s="4">
-        <v>0.1782209738215675</v>
+        <v>178.2209738215675</v>
       </c>
       <c r="P7" s="5">
         <v>18069</v>
@@ -915,10 +938,10 @@
         <v>35</v>
       </c>
       <c r="N8" s="5">
-        <v>200.4390416145325</v>
+        <v>200439.0416145325</v>
       </c>
       <c r="O8" s="4">
-        <v>0.01365574612444015</v>
+        <v>13.65574612444015</v>
       </c>
       <c r="P8" s="5">
         <v>14678</v>
@@ -965,10 +988,10 @@
         <v>35</v>
       </c>
       <c r="N9" s="5">
-        <v>248.6034576892853</v>
+        <v>248603.4576892853</v>
       </c>
       <c r="O9" s="4">
-        <v>0.03339648813665842</v>
+        <v>33.39648813665842</v>
       </c>
       <c r="P9" s="5">
         <v>7444</v>
@@ -1015,10 +1038,10 @@
         <v>35</v>
       </c>
       <c r="N10" s="5">
-        <v>655.3438992500305</v>
+        <v>655343.8992500305</v>
       </c>
       <c r="O10" s="4">
-        <v>0.09956607402765581</v>
+        <v>99.56607402765582</v>
       </c>
       <c r="P10" s="5">
         <v>6582</v>
@@ -1065,10 +1088,10 @@
         <v>35</v>
       </c>
       <c r="N11" s="5">
-        <v>894.3289086818695</v>
+        <v>894328.9086818695</v>
       </c>
       <c r="O11" s="4">
-        <v>0.04007747742244542</v>
+        <v>40.07747742244542</v>
       </c>
       <c r="P11" s="5">
         <v>22315</v>
@@ -1115,10 +1138,10 @@
         <v>35</v>
       </c>
       <c r="N12" s="5">
-        <v>256.0010578632355</v>
+        <v>256001.0578632355</v>
       </c>
       <c r="O12" s="4">
-        <v>0.0185575250353922</v>
+        <v>18.55752503539221</v>
       </c>
       <c r="P12" s="5">
         <v>13795</v>
@@ -1165,10 +1188,10 @@
         <v>35</v>
       </c>
       <c r="N13" s="5">
-        <v>2186.658451080322</v>
+        <v>2186658.451080322</v>
       </c>
       <c r="O13" s="4">
-        <v>0.07477544886230285</v>
+        <v>74.77544886230285</v>
       </c>
       <c r="P13" s="5">
         <v>29243</v>
@@ -1215,10 +1238,10 @@
         <v>35</v>
       </c>
       <c r="N14" s="5">
-        <v>818.4064252376556</v>
+        <v>818406.4252376556</v>
       </c>
       <c r="O14" s="4">
-        <v>0.2366704526424684</v>
+        <v>236.6704526424684</v>
       </c>
       <c r="P14" s="5">
         <v>3458</v>
@@ -1265,10 +1288,10 @@
         <v>35</v>
       </c>
       <c r="N15" s="5">
-        <v>908.2920408248901</v>
+        <v>908292.0408248901</v>
       </c>
       <c r="O15" s="4">
-        <v>0.236657644821493</v>
+        <v>236.657644821493</v>
       </c>
       <c r="P15" s="5">
         <v>3838</v>
@@ -1315,10 +1338,10 @@
         <v>35</v>
       </c>
       <c r="N16" s="5">
-        <v>329.6050052642822</v>
+        <v>329605.0052642822</v>
       </c>
       <c r="O16" s="4">
-        <v>0.09737223198353979</v>
+        <v>97.37223198353979</v>
       </c>
       <c r="P16" s="5">
         <v>3385</v>
@@ -1365,10 +1388,10 @@
         <v>35</v>
       </c>
       <c r="N17" s="5">
-        <v>442.2563414573669</v>
+        <v>442256.3414573669</v>
       </c>
       <c r="O17" s="4">
-        <v>0.09922735953721493</v>
+        <v>99.22735953721492</v>
       </c>
       <c r="P17" s="5">
         <v>4457</v>
@@ -1396,7 +1419,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1407,9 +1430,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1443,8 +1472,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1466,116 +1503,164 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2746615555001622</v>
+        <v>1.218089500220623</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2612098230367268</v>
+        <v>1.02192026862908</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2490085984697137</v>
+        <v>4.714902292009376</v>
       </c>
       <c r="E3" s="4">
-        <v>56.37755102040816</v>
+        <v>68.94132653061224</v>
       </c>
       <c r="F3" s="4">
-        <v>65.12164429530202</v>
+        <v>55.69630872483221</v>
       </c>
       <c r="G3" s="5">
         <v>8</v>
       </c>
       <c r="H3" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I3" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J3" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>1</v>
+      </c>
+      <c r="P3" s="4">
+        <v>1.218089500220623</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>1.02192026862908</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3471930390528728</v>
+        <v>1.262178020419262</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1380849017692962</v>
+        <v>0.9060182164165722</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2833941480438925</v>
+        <v>3.355189646543077</v>
       </c>
       <c r="E4" s="4">
-        <v>57.66581632653061</v>
+        <v>68.58418367346938</v>
       </c>
       <c r="F4" s="4">
-        <v>65.78439597315436</v>
+        <v>56.84563758389262</v>
       </c>
       <c r="G4" s="5">
         <v>8</v>
       </c>
       <c r="H4" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J4" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>2</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.262178020419262</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.9060182164165722</v>
+      </c>
+      <c r="R4" s="5">
+        <v>2</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.2771045802871596</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.10100955748024</v>
-      </c>
+        <v>3.615707080292309</v>
+      </c>
+      <c r="C5" s="4"/>
       <c r="D5" s="4">
-        <v>0.2939561055397077</v>
+        <v>7.57648836458444</v>
       </c>
       <c r="E5" s="4">
-        <v>57.5</v>
+        <v>61.98129251700681</v>
       </c>
       <c r="F5" s="4">
-        <v>66.42617449664429</v>
+        <v>53.66051454138711</v>
       </c>
       <c r="G5" s="5">
         <v>8</v>
       </c>
       <c r="H5" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I5" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J5" s="5">
         <v>3</v>
@@ -1584,96 +1669,140 @@
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+        <v>1</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="4">
+        <v>3.615707080292309</v>
+      </c>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="5">
+        <v>0</v>
+      </c>
+      <c r="S5" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.2258044283367856</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0.1461440169314326</v>
-      </c>
+        <v>4.418034630689792</v>
+      </c>
+      <c r="C6" s="4"/>
       <c r="D6" s="4">
-        <v>0.2209092781002491</v>
+        <v>8.710875297601712</v>
       </c>
       <c r="E6" s="4">
-        <v>45.7653061224492</v>
+        <v>58.82653061224453</v>
       </c>
       <c r="F6" s="4">
-        <v>55.70469798657707</v>
+        <v>54.82102908277395</v>
       </c>
       <c r="G6" s="5">
         <v>6</v>
       </c>
       <c r="H6" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I6" s="5">
         <v>0</v>
       </c>
       <c r="J6" s="5">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K6" s="5">
         <v>0</v>
       </c>
       <c r="L6" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M6" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+        <v>1</v>
+      </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>1</v>
+      </c>
+      <c r="P6" s="4">
+        <v>4.418034630689792</v>
+      </c>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="5">
+        <v>0</v>
+      </c>
+      <c r="S6" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B7" s="4">
-        <v>0.7836699380193732</v>
+        <v>0.2238663620238519</v>
       </c>
       <c r="C7" s="4">
-        <v>0.3604053583884748</v>
+        <v>0.2238663620238519</v>
       </c>
       <c r="D7" s="4">
-        <v>0.7937801347810695</v>
+        <v>0.2653326361232615</v>
       </c>
       <c r="E7" s="4">
-        <v>37.06122448979592</v>
+        <v>86.57142857142857</v>
       </c>
       <c r="F7" s="4">
-        <v>46.42281879194631</v>
+        <v>88.67785234899328</v>
       </c>
       <c r="G7" s="5">
         <v>5</v>
       </c>
       <c r="H7" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I7" s="5">
         <v>0</v>
       </c>
       <c r="J7" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K7" s="5">
         <v>0</v>
       </c>
       <c r="L7" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M7" s="5">
         <v>0</v>
       </c>
+      <c r="N7" s="4">
+        <v>-0.2238663620238519</v>
+      </c>
+      <c r="O7" s="5">
+        <v>5</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.1736692103147292</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.1736692103147292</v>
+      </c>
+      <c r="R7" s="5">
+        <v>5</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1684,6 +1813,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1691,7 +1821,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1702,9 +1832,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1738,8 +1874,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1761,214 +1905,310 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>5.874943581321117</v>
+        <v>0.281843700340459</v>
       </c>
       <c r="C3" s="4">
-        <v>0</v>
+        <v>0.2267154500439453</v>
       </c>
       <c r="D3" s="4">
-        <v>19.38239392349946</v>
+        <v>0.8192100905687304</v>
       </c>
       <c r="E3" s="4">
-        <v>63.7202380952384</v>
+        <v>60.82057823129251</v>
       </c>
       <c r="F3" s="4">
-        <v>54.43372483221476</v>
+        <v>61.84144295302013</v>
       </c>
       <c r="G3" s="5">
         <v>8</v>
       </c>
       <c r="H3" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I3" s="5">
+        <v>1</v>
+      </c>
+      <c r="J3" s="5">
+        <v>3</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>3</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
         <v>4</v>
       </c>
-      <c r="J3" s="5">
+      <c r="P3" s="4">
+        <v>0.281843700340459</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2267154500439453</v>
+      </c>
+      <c r="R3" s="5">
         <v>4</v>
       </c>
-      <c r="K3" s="5">
-        <v>2</v>
-      </c>
-      <c r="L3" s="5">
-        <v>2</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>5.180882168479738</v>
+        <v>0.8366957389368213</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3905383204884336</v>
+        <v>0.7545632904838184</v>
       </c>
       <c r="D4" s="4">
-        <v>12.99208016461926</v>
+        <v>1.003677412206875</v>
       </c>
       <c r="E4" s="4">
-        <v>69.05187074829931</v>
+        <v>68.41836734693878</v>
       </c>
       <c r="F4" s="4">
-        <v>63.24804250559285</v>
+        <v>70.50055928411632</v>
       </c>
       <c r="G4" s="5">
         <v>8</v>
       </c>
       <c r="H4" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I4" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J4" s="5">
+        <v>3</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>3</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
         <v>4</v>
       </c>
-      <c r="K4" s="5">
-        <v>3</v>
-      </c>
-      <c r="L4" s="5">
-        <v>1</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="P4" s="4">
+        <v>0.8366957389368213</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.7545632904838184</v>
+      </c>
+      <c r="R4" s="5">
+        <v>4</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>4.004698797399746</v>
+        <v>1.681096878745434</v>
       </c>
       <c r="C5" s="4">
-        <v>0.7391134515976757</v>
+        <v>1.466332825573694</v>
       </c>
       <c r="D5" s="4">
-        <v>10.69890789621566</v>
+        <v>2.085915413596508</v>
       </c>
       <c r="E5" s="4">
-        <v>73.46938775510205</v>
+        <v>64.26870748299307</v>
       </c>
       <c r="F5" s="4">
-        <v>72.67058165548097</v>
+        <v>66.91694630872432</v>
       </c>
       <c r="G5" s="5">
         <v>8</v>
       </c>
       <c r="H5" s="5">
+        <v>5</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
         <v>3</v>
       </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>5</v>
-      </c>
       <c r="K5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M5" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>1.466332825573694</v>
+      </c>
+      <c r="O5" s="5">
+        <v>5</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.5274361210362141</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.33973706038509</v>
+      </c>
+      <c r="R5" s="5">
+        <v>5</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>15.265517181156</v>
+        <v>2.283423370120844</v>
       </c>
       <c r="C6" s="4">
-        <v>0</v>
+        <v>1.84475266177111</v>
       </c>
       <c r="D6" s="4">
-        <v>26.13396019339355</v>
+        <v>2.737409855919997</v>
       </c>
       <c r="E6" s="4">
-        <v>55.58390022675764</v>
+        <v>60.45918367346934</v>
       </c>
       <c r="F6" s="4">
-        <v>52.11222967934356</v>
+        <v>62.01715137956734</v>
       </c>
       <c r="G6" s="5">
         <v>6</v>
       </c>
       <c r="H6" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" s="5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K6" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L6" s="5">
+        <v>3</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
         <v>2</v>
       </c>
-      <c r="M6" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="P6" s="4">
+        <v>2.283423370120844</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>1.84475266177111</v>
+      </c>
+      <c r="R6" s="5">
+        <v>2</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B7" s="4">
-        <v>0.2488572493986957</v>
-      </c>
-      <c r="C7" s="4">
-        <v>0.2488572493986957</v>
-      </c>
+        <v>0.5522014037566059</v>
+      </c>
+      <c r="C7" s="4"/>
       <c r="D7" s="4">
-        <v>0.201104869027602</v>
+        <v>0.6244008554576708</v>
       </c>
       <c r="E7" s="4">
-        <v>87.08163265306122</v>
+        <v>53.6530612244898</v>
       </c>
       <c r="F7" s="4">
-        <v>86.04697986577182</v>
+        <v>48.48322147651007</v>
       </c>
       <c r="G7" s="5">
         <v>5</v>
       </c>
       <c r="H7" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I7" s="5">
         <v>0</v>
       </c>
       <c r="J7" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K7" s="5">
         <v>0</v>
       </c>
       <c r="L7" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M7" s="5">
         <v>0</v>
       </c>
+      <c r="N7" s="4"/>
+      <c r="O7" s="5">
+        <v>0</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.5522014037566059</v>
+      </c>
+      <c r="Q7" s="4"/>
+      <c r="R7" s="5">
+        <v>0</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1979,6 +2219,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1986,7 +2227,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1997,9 +2238,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2033,8 +2280,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2056,214 +2311,316 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>5.753891792991039</v>
+        <v>0.3471930390528728</v>
       </c>
       <c r="C3" s="4">
-        <v>0</v>
+        <v>0.1380849017692962</v>
       </c>
       <c r="D3" s="4">
-        <v>10.59917911598908</v>
+        <v>0.2833941480438925</v>
       </c>
       <c r="E3" s="4">
-        <v>68.92431972789142</v>
+        <v>57.66581632653061</v>
       </c>
       <c r="F3" s="4">
-        <v>60.99552572707024</v>
+        <v>65.78439597315436</v>
       </c>
       <c r="G3" s="5">
         <v>8</v>
       </c>
       <c r="H3" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
         <v>3</v>
       </c>
-      <c r="J3" s="5">
-        <v>5</v>
-      </c>
       <c r="K3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" s="5">
         <v>3</v>
       </c>
       <c r="M3" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.04844509037226263</v>
+      </c>
+      <c r="O3" s="5">
+        <v>5</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3471930390528728</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1477739198437487</v>
+      </c>
+      <c r="R3" s="5">
+        <v>5</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>2.69607420034009</v>
+        <v>0.2771045802871596</v>
       </c>
       <c r="C4" s="4">
-        <v>0</v>
+        <v>0.10100955748024</v>
       </c>
       <c r="D4" s="4">
-        <v>9.196826649375733</v>
+        <v>0.2939561055397077</v>
       </c>
       <c r="E4" s="4">
-        <v>56.39455782312929</v>
+        <v>57.5</v>
       </c>
       <c r="F4" s="4">
-        <v>48.71504474272979</v>
+        <v>66.42617449664429</v>
       </c>
       <c r="G4" s="5">
         <v>8</v>
       </c>
       <c r="H4" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I4" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J4" s="5">
         <v>3</v>
       </c>
       <c r="K4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.0833285650383371</v>
+      </c>
+      <c r="O4" s="5">
+        <v>5</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.295631082677642</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.08065482228200971</v>
+      </c>
+      <c r="R4" s="5">
+        <v>5</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>2.717896505529629</v>
+        <v>0.2746615555001622</v>
       </c>
       <c r="C5" s="4">
-        <v>1.594346904872207</v>
+        <v>0.2612098230367268</v>
       </c>
       <c r="D5" s="4">
-        <v>6.538589521581875</v>
+        <v>0.2490085984697137</v>
       </c>
       <c r="E5" s="4">
-        <v>67.24489795918366</v>
+        <v>56.37755102040816</v>
       </c>
       <c r="F5" s="4">
-        <v>59.9398769574944</v>
+        <v>65.12164429530202</v>
       </c>
       <c r="G5" s="5">
         <v>8</v>
       </c>
       <c r="H5" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I5" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J5" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>4</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2746615555001622</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2612098230367268</v>
+      </c>
+      <c r="R5" s="5">
+        <v>4</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>5.423248555260817</v>
+        <v>0.2258044283367856</v>
       </c>
       <c r="C6" s="4">
-        <v>0</v>
+        <v>0.1461440169314326</v>
       </c>
       <c r="D6" s="4">
-        <v>11.49799246191772</v>
+        <v>0.2209092781002491</v>
       </c>
       <c r="E6" s="4">
-        <v>64.76757369614442</v>
+        <v>45.7653061224492</v>
       </c>
       <c r="F6" s="4">
-        <v>63.28859060402829</v>
+        <v>55.70469798657707</v>
       </c>
       <c r="G6" s="5">
         <v>6</v>
       </c>
       <c r="H6" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I6" s="5">
         <v>0</v>
       </c>
       <c r="J6" s="5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
         <v>3</v>
       </c>
-      <c r="L6" s="5">
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>3</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.2258044283367856</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.1461440169314326</v>
+      </c>
+      <c r="R6" s="5">
+        <v>3</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" s="4">
+        <v>0.7836699380193732</v>
+      </c>
+      <c r="C7" s="4">
+        <v>0.3604053583884748</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0.7937801347810695</v>
+      </c>
+      <c r="E7" s="4">
+        <v>37.06122448979592</v>
+      </c>
+      <c r="F7" s="4">
+        <v>46.42281879194631</v>
+      </c>
+      <c r="G7" s="5">
+        <v>5</v>
+      </c>
+      <c r="H7" s="5">
         <v>2</v>
       </c>
-      <c r="M6" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
-      <c r="A7" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B7" s="4">
-        <v>0.2751613725751255</v>
-      </c>
-      <c r="C7" s="4">
-        <v>0.2453251673345566</v>
-      </c>
-      <c r="D7" s="4">
-        <v>0.310547839555106</v>
-      </c>
-      <c r="E7" s="4">
-        <v>87.44217687074831</v>
-      </c>
-      <c r="F7" s="4">
-        <v>84.98881431767336</v>
-      </c>
-      <c r="G7" s="5">
-        <v>5</v>
-      </c>
-      <c r="H7" s="5">
-        <v>4</v>
-      </c>
       <c r="I7" s="5">
         <v>0</v>
       </c>
       <c r="J7" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K7" s="5">
         <v>0</v>
       </c>
       <c r="L7" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M7" s="5">
         <v>0</v>
       </c>
+      <c r="N7" s="4"/>
+      <c r="O7" s="5">
+        <v>2</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.7836699380193732</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.3604053583884748</v>
+      </c>
+      <c r="R7" s="5">
+        <v>2</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2274,6 +2631,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2281,7 +2639,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2292,9 +2650,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2328,8 +2692,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2351,107 +2723,157 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>7.919453469016429</v>
+        <v>5.180882168479738</v>
       </c>
       <c r="C3" s="4">
-        <v>0</v>
+        <v>0.3905383204884336</v>
       </c>
       <c r="D3" s="4">
-        <v>14.26541337082612</v>
+        <v>12.99208016461926</v>
       </c>
       <c r="E3" s="4">
-        <v>64.88095238095276</v>
+        <v>69.05187074829931</v>
       </c>
       <c r="F3" s="4">
-        <v>64.4742729306496</v>
+        <v>63.24804250559285</v>
       </c>
       <c r="G3" s="5">
         <v>8</v>
       </c>
       <c r="H3" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J3" s="5">
         <v>4</v>
       </c>
       <c r="K3" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>5.180882168479738</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3905383204884336</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>1.344007206626711</v>
+        <v>4.004698797399746</v>
       </c>
       <c r="C4" s="4">
-        <v>0</v>
+        <v>0.7391134515976757</v>
       </c>
       <c r="D4" s="4">
-        <v>11.4454340464552</v>
+        <v>10.69890789621566</v>
       </c>
       <c r="E4" s="4">
-        <v>48.03571428571453</v>
+        <v>73.46938775510205</v>
       </c>
       <c r="F4" s="4">
-        <v>47.18260626398262</v>
+        <v>72.67058165548097</v>
       </c>
       <c r="G4" s="5">
         <v>8</v>
       </c>
       <c r="H4" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>5</v>
+      </c>
+      <c r="K4" s="5">
+        <v>1</v>
+      </c>
+      <c r="L4" s="5">
+        <v>2</v>
+      </c>
+      <c r="M4" s="5">
+        <v>2</v>
+      </c>
+      <c r="N4" s="4">
+        <v>2.251121085974801</v>
+      </c>
+      <c r="O4" s="5">
+        <v>5</v>
+      </c>
+      <c r="P4" s="4">
+        <v>3.401776238621899</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>1.361709744709979</v>
+      </c>
+      <c r="R4" s="5">
         <v>3</v>
       </c>
-      <c r="J4" s="5">
-        <v>5</v>
-      </c>
-      <c r="K4" s="5">
-        <v>5</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="S4" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>1.810451551611172</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0</v>
-      </c>
+        <v>5.874943581321117</v>
+      </c>
+      <c r="C5" s="4"/>
       <c r="D5" s="4">
-        <v>10.11134247415756</v>
+        <v>19.38239392349946</v>
       </c>
       <c r="E5" s="4">
-        <v>52.33418367346944</v>
+        <v>63.7202380952384</v>
       </c>
       <c r="F5" s="4">
-        <v>50.2321029082774</v>
+        <v>54.43372483221476</v>
       </c>
       <c r="G5" s="5">
         <v>8</v>
@@ -2460,39 +2882,51 @@
         <v>0</v>
       </c>
       <c r="I5" s="5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J5" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K5" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L5" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>0</v>
+      </c>
+      <c r="P5" s="4">
+        <v>5.874943581321117</v>
+      </c>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="5">
+        <v>0</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>7.896906799075921</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0</v>
-      </c>
+        <v>15.265517181156</v>
+      </c>
+      <c r="C6" s="4"/>
       <c r="D6" s="4">
-        <v>16.34532048900716</v>
+        <v>26.13396019339355</v>
       </c>
       <c r="E6" s="4">
-        <v>55.00566893424087</v>
+        <v>55.58390022675764</v>
       </c>
       <c r="F6" s="4">
-        <v>54.87509321401981</v>
+        <v>52.11222967934356</v>
       </c>
       <c r="G6" s="5">
         <v>6</v>
@@ -2507,33 +2941,47 @@
         <v>6</v>
       </c>
       <c r="K6" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L6" s="5">
         <v>2</v>
       </c>
       <c r="M6" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+        <v>0</v>
+      </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>0</v>
+      </c>
+      <c r="P6" s="4">
+        <v>15.265517181156</v>
+      </c>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="5">
+        <v>0</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B7" s="4">
-        <v>0.1570119102968839</v>
+        <v>0.2488572493986957</v>
       </c>
       <c r="C7" s="4">
-        <v>0.1570119102968839</v>
+        <v>0.2488572493986957</v>
       </c>
       <c r="D7" s="4">
-        <v>0.1633298982709263</v>
+        <v>0.201104869027602</v>
       </c>
       <c r="E7" s="4">
-        <v>86.57142857142857</v>
+        <v>87.08163265306122</v>
       </c>
       <c r="F7" s="4">
-        <v>89.40939597315436</v>
+        <v>86.04697986577182</v>
       </c>
       <c r="G7" s="5">
         <v>5</v>
@@ -2556,9 +3004,27 @@
       <c r="M7" s="5">
         <v>0</v>
       </c>
+      <c r="N7" s="4">
+        <v>-0.2488572493986957</v>
+      </c>
+      <c r="O7" s="5">
+        <v>5</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.125298696245624</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.125298696245624</v>
+      </c>
+      <c r="R7" s="5">
+        <v>5</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2569,6 +3035,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2576,7 +3043,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2587,9 +3054,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2623,8 +3096,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2646,214 +3127,300 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.1712960702412257</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.1841122212775715</v>
-      </c>
+        <v>2.69607420034009</v>
+      </c>
+      <c r="C3" s="4"/>
       <c r="D3" s="4">
-        <v>0.1683527202390526</v>
+        <v>9.196826649375733</v>
       </c>
       <c r="E3" s="4">
-        <v>90.96938775510205</v>
+        <v>56.39455782312929</v>
       </c>
       <c r="F3" s="4">
-        <v>92.79502237136467</v>
+        <v>48.71504474272979</v>
       </c>
       <c r="G3" s="5">
         <v>8</v>
       </c>
       <c r="H3" s="5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J3" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>0</v>
+      </c>
+      <c r="P3" s="4">
+        <v>2.69607420034009</v>
+      </c>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="5">
+        <v>0</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3056473376656078</v>
+        <v>2.717896505529629</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2146686977135578</v>
+        <v>1.594346904872207</v>
       </c>
       <c r="D4" s="4">
-        <v>0.1939560415649842</v>
+        <v>6.538589521581875</v>
       </c>
       <c r="E4" s="4">
-        <v>87.14710884353741</v>
+        <v>67.24489795918366</v>
       </c>
       <c r="F4" s="4">
-        <v>85.99832214765101</v>
+        <v>59.9398769574944</v>
       </c>
       <c r="G4" s="5">
         <v>8</v>
       </c>
       <c r="H4" s="5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J4" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>2.717896505529629</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>1.594346904872207</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.156696567715244</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.156696567715244</v>
-      </c>
+        <v>5.753891792991039</v>
+      </c>
+      <c r="C5" s="4"/>
       <c r="D5" s="4">
-        <v>0.1681418678975891</v>
+        <v>10.59917911598908</v>
       </c>
       <c r="E5" s="4">
-        <v>90.54846938775511</v>
+        <v>68.92431972789142</v>
       </c>
       <c r="F5" s="4">
-        <v>93.09144295302013</v>
+        <v>60.99552572707024</v>
       </c>
       <c r="G5" s="5">
         <v>8</v>
       </c>
       <c r="H5" s="5">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I5" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J5" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+        <v>1</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="4">
+        <v>5.753891792991039</v>
+      </c>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="5">
+        <v>0</v>
+      </c>
+      <c r="S5" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.2324208387842933</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0.2324208387842933</v>
-      </c>
+        <v>5.423248555260817</v>
+      </c>
+      <c r="C6" s="4"/>
       <c r="D6" s="4">
-        <v>0.2726775716674648</v>
+        <v>11.49799246191772</v>
       </c>
       <c r="E6" s="4">
-        <v>87.43197278911559</v>
+        <v>64.76757369614442</v>
       </c>
       <c r="F6" s="4">
-        <v>90.77740492170031</v>
+        <v>63.28859060402829</v>
       </c>
       <c r="G6" s="5">
         <v>6</v>
       </c>
       <c r="H6" s="5">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
         <v>6</v>
       </c>
-      <c r="I6" s="5">
-        <v>0</v>
-      </c>
-      <c r="J6" s="5">
-        <v>0</v>
-      </c>
       <c r="K6" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L6" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M6" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+        <v>1</v>
+      </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>1</v>
+      </c>
+      <c r="P6" s="4">
+        <v>5.423248555260817</v>
+      </c>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="5">
+        <v>0</v>
+      </c>
+      <c r="S6" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B7" s="4">
-        <v>0.386882423314411</v>
+        <v>0.2751613725751255</v>
       </c>
       <c r="C7" s="4">
-        <v>0.386882423314411</v>
+        <v>0.2453251673345566</v>
       </c>
       <c r="D7" s="4">
-        <v>0.5235765923589113</v>
+        <v>0.310547839555106</v>
       </c>
       <c r="E7" s="4">
-        <v>85.63265306122449</v>
+        <v>87.44217687074831</v>
       </c>
       <c r="F7" s="4">
-        <v>88.5503355704698</v>
+        <v>84.98881431767336</v>
       </c>
       <c r="G7" s="5">
         <v>5</v>
       </c>
       <c r="H7" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I7" s="5">
         <v>0</v>
       </c>
       <c r="J7" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" s="5">
         <v>0</v>
       </c>
       <c r="L7" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" s="5">
         <v>0</v>
       </c>
+      <c r="N7" s="4"/>
+      <c r="O7" s="5">
+        <v>4</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.2751613725751255</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.2453251673345566</v>
+      </c>
+      <c r="R7" s="5">
+        <v>4</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2864,6 +3431,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2871,7 +3439,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2882,9 +3450,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2918,8 +3492,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2941,40 +3523,56 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3704420431472201</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.3574024363634948</v>
-      </c>
+        <v>1.344007206626711</v>
+      </c>
+      <c r="C3" s="4"/>
       <c r="D3" s="4">
-        <v>0.3370538680769201</v>
+        <v>11.4454340464552</v>
       </c>
       <c r="E3" s="4">
-        <v>88.72448979591837</v>
+        <v>48.03571428571453</v>
       </c>
       <c r="F3" s="4">
-        <v>88.27740492170025</v>
+        <v>47.18260626398262</v>
       </c>
       <c r="G3" s="5">
         <v>8</v>
       </c>
       <c r="H3" s="5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I3" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J3" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K3" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L3" s="5">
         <v>0</v>
@@ -2982,35 +3580,47 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>0</v>
+      </c>
+      <c r="P3" s="4">
+        <v>1.344007206626711</v>
+      </c>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="5">
+        <v>0</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.7472034818376162</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.6355511842034739</v>
-      </c>
+        <v>1.810451551611172</v>
+      </c>
+      <c r="C4" s="4"/>
       <c r="D4" s="4">
-        <v>0.6017360486904944</v>
+        <v>10.11134247415756</v>
       </c>
       <c r="E4" s="4">
-        <v>86.68367346938776</v>
+        <v>52.33418367346944</v>
       </c>
       <c r="F4" s="4">
-        <v>82.66079418344519</v>
+        <v>50.2321029082774</v>
       </c>
       <c r="G4" s="5">
         <v>8</v>
       </c>
       <c r="H4" s="5">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5">
         <v>7</v>
       </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
       <c r="J4" s="5">
         <v>1</v>
       </c>
@@ -3023,107 +3633,145 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>0</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.810451551611172</v>
+      </c>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="5">
+        <v>0</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.3857773055410108</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.3857773055410108</v>
-      </c>
+        <v>7.919453469016429</v>
+      </c>
+      <c r="C5" s="4"/>
       <c r="D5" s="4">
-        <v>0.3927960476925478</v>
+        <v>14.26541337082612</v>
       </c>
       <c r="E5" s="4">
-        <v>92.1045918367347</v>
+        <v>64.88095238095276</v>
       </c>
       <c r="F5" s="4">
-        <v>93.73741610738254</v>
+        <v>64.4742729306496</v>
       </c>
       <c r="G5" s="5">
         <v>8</v>
       </c>
       <c r="H5" s="5">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I5" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J5" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" s="5">
         <v>0</v>
       </c>
       <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+        <v>3</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>3</v>
+      </c>
+      <c r="P5" s="4">
+        <v>7.91945346901643</v>
+      </c>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="5">
+        <v>0</v>
+      </c>
+      <c r="S5" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.09810265736997126</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0.09810265736997126</v>
-      </c>
+        <v>7.896906799075921</v>
+      </c>
+      <c r="C6" s="4"/>
       <c r="D6" s="4">
-        <v>0.09071028070867533</v>
+        <v>16.34532048900716</v>
       </c>
       <c r="E6" s="4">
-        <v>89.50680272108843</v>
+        <v>55.00566893424087</v>
       </c>
       <c r="F6" s="4">
-        <v>92.19239373601791</v>
+        <v>54.87509321401981</v>
       </c>
       <c r="G6" s="5">
         <v>6</v>
       </c>
       <c r="H6" s="5">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
         <v>6</v>
       </c>
-      <c r="I6" s="5">
-        <v>0</v>
-      </c>
-      <c r="J6" s="5">
-        <v>0</v>
-      </c>
       <c r="K6" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L6" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M6" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+        <v>1</v>
+      </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>1</v>
+      </c>
+      <c r="P6" s="4">
+        <v>7.896906799075921</v>
+      </c>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="5">
+        <v>0</v>
+      </c>
+      <c r="S6" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B7" s="4">
-        <v>0.5569618359999445</v>
+        <v>0.1570119102968839</v>
       </c>
       <c r="C7" s="4">
-        <v>0.5569618359999445</v>
+        <v>0.1570119102968839</v>
       </c>
       <c r="D7" s="4">
-        <v>0.5638918534712694</v>
+        <v>0.1633298982709263</v>
       </c>
       <c r="E7" s="4">
-        <v>89.08163265306122</v>
+        <v>86.57142857142857</v>
       </c>
       <c r="F7" s="4">
-        <v>91.85234899328859</v>
+        <v>89.40939597315436</v>
       </c>
       <c r="G7" s="5">
         <v>5</v>
@@ -3146,9 +3794,27 @@
       <c r="M7" s="5">
         <v>0</v>
       </c>
+      <c r="N7" s="4">
+        <v>-0.1196320907072895</v>
+      </c>
+      <c r="O7" s="5">
+        <v>5</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.155783922393409</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.155783922393409</v>
+      </c>
+      <c r="R7" s="5">
+        <v>5</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3159,6 +3825,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3166,7 +3833,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3177,9 +3844,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3213,8 +3886,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3236,148 +3917,220 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2263585859023462</v>
+        <v>0.3056473376656078</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2263585859023462</v>
+        <v>0.2146686977135578</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2306020231031309</v>
+        <v>0.1939560415649842</v>
       </c>
       <c r="E3" s="4">
-        <v>90.70153061224489</v>
+        <v>87.14710884353741</v>
       </c>
       <c r="F3" s="4">
-        <v>92.42030201342281</v>
+        <v>85.99832214765101</v>
       </c>
       <c r="G3" s="5">
         <v>8</v>
       </c>
       <c r="H3" s="5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.03158541790023504</v>
+      </c>
+      <c r="O3" s="5">
+        <v>7</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.297750983190549</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2011320900420285</v>
+      </c>
+      <c r="R3" s="5">
+        <v>7</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3335679265701784</v>
+        <v>0.156696567715244</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2435430056456787</v>
+        <v>0.156696567715244</v>
       </c>
       <c r="D4" s="4">
-        <v>0.232678556671189</v>
+        <v>0.1681418678975891</v>
       </c>
       <c r="E4" s="4">
-        <v>88.04421768707483</v>
+        <v>90.54846938775511</v>
       </c>
       <c r="F4" s="4">
-        <v>86.40100671140939</v>
+        <v>93.09144295302013</v>
       </c>
       <c r="G4" s="5">
         <v>8</v>
       </c>
       <c r="H4" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.05163051121924545</v>
+      </c>
+      <c r="O4" s="5">
+        <v>8</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.142060779132386</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.142060779132386</v>
+      </c>
+      <c r="R4" s="5">
+        <v>8</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.1655423667331808</v>
+        <v>0.1712960702412257</v>
       </c>
       <c r="C5" s="4">
-        <v>0.1655423667331808</v>
+        <v>0.1841122212775715</v>
       </c>
       <c r="D5" s="4">
-        <v>0.1764350630651529</v>
+        <v>0.1683527202390526</v>
       </c>
       <c r="E5" s="4">
-        <v>91.19897959183673</v>
+        <v>90.96938775510205</v>
       </c>
       <c r="F5" s="4">
-        <v>92.68456375838926</v>
+        <v>92.79502237136467</v>
       </c>
       <c r="G5" s="5">
         <v>8</v>
       </c>
       <c r="H5" s="5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4">
+        <v>0.1841122212775715</v>
+      </c>
+      <c r="O5" s="5">
+        <v>7</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.05217117023802196</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.04497716480191564</v>
+      </c>
+      <c r="R5" s="5">
+        <v>7</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.2822124728670874</v>
+        <v>0.2324208387842933</v>
       </c>
       <c r="C6" s="4">
-        <v>0.2822124728670874</v>
+        <v>0.2324208387842933</v>
       </c>
       <c r="D6" s="4">
-        <v>0.3133036207092175</v>
+        <v>0.2726775716674648</v>
       </c>
       <c r="E6" s="4">
-        <v>87.05782312925164</v>
+        <v>87.43197278911559</v>
       </c>
       <c r="F6" s="4">
-        <v>89.5413870246086</v>
+        <v>90.77740492170031</v>
       </c>
       <c r="G6" s="5">
         <v>6</v>
@@ -3400,25 +4153,43 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4">
+        <v>0.1080399215200778</v>
+      </c>
+      <c r="O6" s="5">
+        <v>6</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.1776956906854402</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.1776956906854402</v>
+      </c>
+      <c r="R6" s="5">
+        <v>6</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B7" s="4">
-        <v>0.3527823855012187</v>
+        <v>0.386882423314411</v>
       </c>
       <c r="C7" s="4">
-        <v>0.3527823855012187</v>
+        <v>0.386882423314411</v>
       </c>
       <c r="D7" s="4">
-        <v>0.4993765284150484</v>
+        <v>0.5235765923589113</v>
       </c>
       <c r="E7" s="4">
-        <v>85.85714285714286</v>
+        <v>85.63265306122449</v>
       </c>
       <c r="F7" s="4">
-        <v>88.67114093959732</v>
+        <v>88.5503355704698</v>
       </c>
       <c r="G7" s="5">
         <v>5</v>
@@ -3441,9 +4212,27 @@
       <c r="M7" s="5">
         <v>0</v>
       </c>
+      <c r="N7" s="4">
+        <v>-0.3341589347319477</v>
+      </c>
+      <c r="O7" s="5">
+        <v>5</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.2986022375385617</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.2986022375385617</v>
+      </c>
+      <c r="R7" s="5">
+        <v>5</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3454,6 +4243,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3461,7 +4251,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3472,9 +4262,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3508,8 +4304,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3531,25 +4335,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2209199911845589</v>
+        <v>0.7472034818376162</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1164727271093756</v>
+        <v>0.6355511842034739</v>
       </c>
       <c r="D3" s="4">
-        <v>0.7013970225048888</v>
+        <v>0.6017360486904944</v>
       </c>
       <c r="E3" s="4">
-        <v>87.56377551020408</v>
+        <v>86.68367346938776</v>
       </c>
       <c r="F3" s="4">
-        <v>87.96560402684564</v>
+        <v>82.66079418344519</v>
       </c>
       <c r="G3" s="5">
         <v>8</v>
@@ -3572,66 +4394,102 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.6355511842034739</v>
+      </c>
+      <c r="O3" s="5">
+        <v>7</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1877752162754068</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.08699762130430232</v>
+      </c>
+      <c r="R3" s="5">
+        <v>7</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.4659248166600992</v>
+        <v>0.3857773055410108</v>
       </c>
       <c r="C4" s="4">
-        <v>0.306642234688076</v>
+        <v>0.3857773055410108</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3043514652835205</v>
+        <v>0.3927960476925478</v>
       </c>
       <c r="E4" s="4">
-        <v>83.76275510204081</v>
+        <v>92.1045918367347</v>
       </c>
       <c r="F4" s="4">
-        <v>78.32774049217004</v>
+        <v>93.73741610738254</v>
       </c>
       <c r="G4" s="5">
         <v>8</v>
       </c>
       <c r="H4" s="5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.3857773055410108</v>
+      </c>
+      <c r="O4" s="5">
+        <v>8</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1180431993181073</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1180431993181073</v>
+      </c>
+      <c r="R4" s="5">
+        <v>8</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.2372125254028588</v>
+        <v>0.3704420431472201</v>
       </c>
       <c r="C5" s="4">
-        <v>0.2543891811574024</v>
+        <v>0.3574024363634948</v>
       </c>
       <c r="D5" s="4">
-        <v>0.264385439177721</v>
+        <v>0.3370538680769201</v>
       </c>
       <c r="E5" s="4">
-        <v>89.7704081632653</v>
+        <v>88.72448979591837</v>
       </c>
       <c r="F5" s="4">
-        <v>88.98629753914989</v>
+        <v>88.27740492170025</v>
       </c>
       <c r="G5" s="5">
         <v>8</v>
@@ -3654,66 +4512,102 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4">
+        <v>-0.3574024363634948</v>
+      </c>
+      <c r="O5" s="5">
+        <v>7</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1157885271234613</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1174273375311269</v>
+      </c>
+      <c r="R5" s="5">
+        <v>7</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.09709293154986993</v>
+        <v>0.09810265736997126</v>
       </c>
       <c r="C6" s="4">
-        <v>0.07600013677802162</v>
+        <v>0.09810265736997126</v>
       </c>
       <c r="D6" s="4">
-        <v>0.2326643327851432</v>
+        <v>0.09071028070867533</v>
       </c>
       <c r="E6" s="4">
-        <v>86.85374149659864</v>
+        <v>89.50680272108843</v>
       </c>
       <c r="F6" s="4">
-        <v>88.8366890380312</v>
+        <v>92.19239373601791</v>
       </c>
       <c r="G6" s="5">
         <v>6</v>
       </c>
       <c r="H6" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I6" s="5">
         <v>0</v>
       </c>
       <c r="J6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" s="5">
         <v>0</v>
       </c>
       <c r="L6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4">
+        <v>-0.08978840112892846</v>
+      </c>
+      <c r="O6" s="5">
+        <v>6</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.05721801140843077</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.05721801140843077</v>
+      </c>
+      <c r="R6" s="5">
+        <v>6</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B7" s="4">
-        <v>0.4879506246046922</v>
+        <v>0.5569618359999445</v>
       </c>
       <c r="C7" s="4">
-        <v>0.4879506246046922</v>
+        <v>0.5569618359999445</v>
       </c>
       <c r="D7" s="4">
-        <v>0.4955216363863734</v>
+        <v>0.5638918534712694</v>
       </c>
       <c r="E7" s="4">
-        <v>87.82312925170066</v>
+        <v>89.08163265306122</v>
       </c>
       <c r="F7" s="4">
-        <v>90.70917225950784</v>
+        <v>91.85234899328859</v>
       </c>
       <c r="G7" s="5">
         <v>5</v>
@@ -3736,9 +4630,27 @@
       <c r="M7" s="5">
         <v>0</v>
       </c>
+      <c r="N7" s="4">
+        <v>-0.5569618359999445</v>
+      </c>
+      <c r="O7" s="5">
+        <v>5</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.1969369838993445</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.1969369838993445</v>
+      </c>
+      <c r="R7" s="5">
+        <v>5</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3749,12 +4661,1706 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.3335679265701784</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.2435430056456787</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.232678556671189</v>
+      </c>
+      <c r="E3" s="4">
+        <v>88.04421768707483</v>
+      </c>
+      <c r="F3" s="4">
+        <v>86.40100671140939</v>
+      </c>
+      <c r="G3" s="5">
+        <v>8</v>
+      </c>
+      <c r="H3" s="5">
+        <v>7</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>1</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>1</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.06832744947448431</v>
+      </c>
+      <c r="O3" s="5">
+        <v>7</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.311969160836944</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2090976377399132</v>
+      </c>
+      <c r="R3" s="5">
+        <v>7</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.1655423667331808</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.1655423667331808</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.1764350630651529</v>
+      </c>
+      <c r="E4" s="4">
+        <v>91.19897959183673</v>
+      </c>
+      <c r="F4" s="4">
+        <v>92.68456375838926</v>
+      </c>
+      <c r="G4" s="5">
+        <v>8</v>
+      </c>
+      <c r="H4" s="5">
+        <v>8</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.06716868215297245</v>
+      </c>
+      <c r="O4" s="5">
+        <v>8</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1321151701151775</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1321151701151775</v>
+      </c>
+      <c r="R4" s="5">
+        <v>8</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.2263585859023462</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.2263585859023462</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.2306020231031309</v>
+      </c>
+      <c r="E5" s="4">
+        <v>90.70153061224489</v>
+      </c>
+      <c r="F5" s="4">
+        <v>92.42030201342281</v>
+      </c>
+      <c r="G5" s="5">
+        <v>8</v>
+      </c>
+      <c r="H5" s="5">
+        <v>8</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>0.2263585859023462</v>
+      </c>
+      <c r="O5" s="5">
+        <v>8</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.08870634794495376</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.08870634794495376</v>
+      </c>
+      <c r="R5" s="5">
+        <v>8</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="4">
+        <v>0.2822124728670874</v>
+      </c>
+      <c r="C6" s="4">
+        <v>0.2822124728670874</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0.3133036207092175</v>
+      </c>
+      <c r="E6" s="4">
+        <v>87.05782312925164</v>
+      </c>
+      <c r="F6" s="4">
+        <v>89.5413870246086</v>
+      </c>
+      <c r="G6" s="5">
+        <v>6</v>
+      </c>
+      <c r="H6" s="5">
+        <v>6</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>0</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="4">
+        <v>0.1633263289907809</v>
+      </c>
+      <c r="O6" s="5">
+        <v>6</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.1960584015587261</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.1960584015587261</v>
+      </c>
+      <c r="R6" s="5">
+        <v>6</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" s="4">
+        <v>0.3527823855012187</v>
+      </c>
+      <c r="C7" s="4">
+        <v>0.3527823855012187</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0.4993765284150484</v>
+      </c>
+      <c r="E7" s="4">
+        <v>85.85714285714286</v>
+      </c>
+      <c r="F7" s="4">
+        <v>88.67114093959732</v>
+      </c>
+      <c r="G7" s="5">
+        <v>5</v>
+      </c>
+      <c r="H7" s="5">
+        <v>5</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>0</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="4">
+        <v>-0.2867686823801812</v>
+      </c>
+      <c r="O7" s="5">
+        <v>5</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.2656385324757</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.2656385324757</v>
+      </c>
+      <c r="R7" s="5">
+        <v>5</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.4659248166600992</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.306642234688076</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.3043514652835205</v>
+      </c>
+      <c r="E3" s="4">
+        <v>83.76275510204081</v>
+      </c>
+      <c r="F3" s="4">
+        <v>78.32774049217004</v>
+      </c>
+      <c r="G3" s="5">
+        <v>8</v>
+      </c>
+      <c r="H3" s="5">
+        <v>6</v>
+      </c>
+      <c r="I3" s="5">
+        <v>1</v>
+      </c>
+      <c r="J3" s="5">
+        <v>1</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>1</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.306642234688076</v>
+      </c>
+      <c r="O3" s="5">
+        <v>6</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2154763496946655</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.07492502363018975</v>
+      </c>
+      <c r="R3" s="5">
+        <v>6</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.2372125254028588</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.2543891811574024</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.264385439177721</v>
+      </c>
+      <c r="E4" s="4">
+        <v>89.7704081632653</v>
+      </c>
+      <c r="F4" s="4">
+        <v>88.98629753914989</v>
+      </c>
+      <c r="G4" s="5">
+        <v>8</v>
+      </c>
+      <c r="H4" s="5">
+        <v>7</v>
+      </c>
+      <c r="I4" s="5">
+        <v>1</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.2516801771862278</v>
+      </c>
+      <c r="O4" s="5">
+        <v>7</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1157612938081304</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.07963346259396596</v>
+      </c>
+      <c r="R4" s="5">
+        <v>7</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.2209199911845589</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.1164727271093756</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.7013970225048888</v>
+      </c>
+      <c r="E5" s="4">
+        <v>87.56377551020408</v>
+      </c>
+      <c r="F5" s="4">
+        <v>87.96560402684564</v>
+      </c>
+      <c r="G5" s="5">
+        <v>8</v>
+      </c>
+      <c r="H5" s="5">
+        <v>7</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>1</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>1</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>-0.101802378617934</v>
+      </c>
+      <c r="O5" s="5">
+        <v>7</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2050234273677824</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.08376202865906904</v>
+      </c>
+      <c r="R5" s="5">
+        <v>7</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="4">
+        <v>0.09709293154986993</v>
+      </c>
+      <c r="C6" s="4">
+        <v>0.07600013677802162</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0.2326643327851432</v>
+      </c>
+      <c r="E6" s="4">
+        <v>86.85374149659864</v>
+      </c>
+      <c r="F6" s="4">
+        <v>88.8366890380312</v>
+      </c>
+      <c r="G6" s="5">
+        <v>6</v>
+      </c>
+      <c r="H6" s="5">
+        <v>5</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>1</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>1</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="4">
+        <v>0.07105264241041219</v>
+      </c>
+      <c r="O6" s="5">
+        <v>5</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.06760808223992128</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.05482884608816564</v>
+      </c>
+      <c r="R6" s="5">
+        <v>5</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" s="4">
+        <v>0.4879506246046922</v>
+      </c>
+      <c r="C7" s="4">
+        <v>0.4879506246046922</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0.4955216363863734</v>
+      </c>
+      <c r="E7" s="4">
+        <v>87.82312925170066</v>
+      </c>
+      <c r="F7" s="4">
+        <v>90.70917225950784</v>
+      </c>
+      <c r="G7" s="5">
+        <v>5</v>
+      </c>
+      <c r="H7" s="5">
+        <v>5</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>0</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="4">
+        <v>-0.4879506246046922</v>
+      </c>
+      <c r="O7" s="5">
+        <v>5</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.1874061773579039</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.1874061773579039</v>
+      </c>
+      <c r="R7" s="5">
+        <v>5</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="C3" s="3">
+        <v>31.42857142857143</v>
+      </c>
+      <c r="D3" s="3">
+        <v>51.42857142857142</v>
+      </c>
+      <c r="E3" s="3">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="F3" s="3">
+        <v>37.14285714285715</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>2.795462360646948</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.4889903634597823</v>
+      </c>
+      <c r="J3" s="4">
+        <v>9.365431923431879</v>
+      </c>
+      <c r="K3" s="4">
+        <v>61.79203109815356</v>
+      </c>
+      <c r="L3" s="4">
+        <v>57.81687440076745</v>
+      </c>
+      <c r="M3" s="5">
+        <v>35</v>
+      </c>
+      <c r="N3" s="5">
+        <v>1128843.299865723</v>
+      </c>
+      <c r="O3" s="4">
+        <v>31.68327204989539</v>
+      </c>
+      <c r="P3" s="5">
+        <v>35629</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>74.28571428571429</v>
+      </c>
+      <c r="C4" s="3">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="D4" s="3">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.3357273676477669</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.3286975201185556</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0.3406785833467037</v>
+      </c>
+      <c r="K4" s="4">
+        <v>78.41982507288624</v>
+      </c>
+      <c r="L4" s="4">
+        <v>80.57750079897771</v>
+      </c>
+      <c r="M4" s="5">
+        <v>35</v>
+      </c>
+      <c r="N4" s="5">
+        <v>269772.4313735962</v>
+      </c>
+      <c r="O4" s="4">
+        <v>45.91089710238193</v>
+      </c>
+      <c r="P4" s="5">
+        <v>5876</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3">
+        <v>82.85714285714286</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="E5" s="3">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="F5" s="3">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="G5" s="3">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.5690761662248479</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.2907554371978988</v>
+      </c>
+      <c r="J5" s="4">
+        <v>1.150419670920619</v>
+      </c>
+      <c r="K5" s="4">
+        <v>82.68804664723042</v>
+      </c>
+      <c r="L5" s="4">
+        <v>83.33684883349534</v>
+      </c>
+      <c r="M5" s="5">
+        <v>35</v>
+      </c>
+      <c r="N5" s="5">
+        <v>1035844.679117203</v>
+      </c>
+      <c r="O5" s="4">
+        <v>147.2206763952818</v>
+      </c>
+      <c r="P5" s="5">
+        <v>7036</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3">
+        <v>51.42857142857142</v>
+      </c>
+      <c r="C6" s="3">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="D6" s="3">
+        <v>34.28571428571428</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>34.28571428571428</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.5017780960031494</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.4186488217914645</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0.7806597827537098</v>
+      </c>
+      <c r="K6" s="4">
+        <v>76.75024295432452</v>
+      </c>
+      <c r="L6" s="4">
+        <v>77.31543624161233</v>
+      </c>
+      <c r="M6" s="5">
+        <v>35</v>
+      </c>
+      <c r="N6" s="5">
+        <v>469968.4545993805</v>
+      </c>
+      <c r="O6" s="4">
+        <v>81.12695573957889</v>
+      </c>
+      <c r="P6" s="5">
+        <v>5793</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3">
+        <v>51.42857142857142</v>
+      </c>
+      <c r="C7" s="3">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="D7" s="3">
+        <v>45.71428571428572</v>
+      </c>
+      <c r="E7" s="3">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="F7" s="3">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="G7" s="3">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="H7" s="4">
+        <v>2.193905382133351</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.3661452809632403</v>
+      </c>
+      <c r="J7" s="4">
+        <v>7.02330177644058</v>
+      </c>
+      <c r="K7" s="4">
+        <v>74.16520894071911</v>
+      </c>
+      <c r="L7" s="4">
+        <v>74.34483860658381</v>
+      </c>
+      <c r="M7" s="5">
+        <v>35</v>
+      </c>
+      <c r="N7" s="5">
+        <v>3220274.775981903</v>
+      </c>
+      <c r="O7" s="4">
+        <v>178.2209738215675</v>
+      </c>
+      <c r="P7" s="5">
+        <v>18069</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="C8" s="3">
+        <v>45.71428571428572</v>
+      </c>
+      <c r="D8" s="3">
+        <v>31.42857142857143</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>25.71428571428571</v>
+      </c>
+      <c r="G8" s="3">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="H8" s="4">
+        <v>2.175552875519142</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.4627878441294838</v>
+      </c>
+      <c r="J8" s="4">
+        <v>5.095670986603451</v>
+      </c>
+      <c r="K8" s="4">
+        <v>68.05344995140923</v>
+      </c>
+      <c r="L8" s="4">
+        <v>60.05528922978636</v>
+      </c>
+      <c r="M8" s="5">
+        <v>35</v>
+      </c>
+      <c r="N8" s="5">
+        <v>200439.0416145325</v>
+      </c>
+      <c r="O8" s="4">
+        <v>13.65574612444015</v>
+      </c>
+      <c r="P8" s="5">
+        <v>14678</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3">
+        <v>42.85714285714285</v>
+      </c>
+      <c r="C9" s="3">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="D9" s="3">
+        <v>48.57142857142857</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
+        <v>48.57142857142857</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0.8465529063433157</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0.620887039171915</v>
+      </c>
+      <c r="J9" s="4">
+        <v>1.160357923107193</v>
+      </c>
+      <c r="K9" s="4">
+        <v>62.25947521865874</v>
+      </c>
+      <c r="L9" s="4">
+        <v>63.10258868648114</v>
+      </c>
+      <c r="M9" s="5">
+        <v>35</v>
+      </c>
+      <c r="N9" s="5">
+        <v>248603.4576892853</v>
+      </c>
+      <c r="O9" s="4">
+        <v>33.39648813665842</v>
+      </c>
+      <c r="P9" s="5">
+        <v>7444</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3">
+        <v>54.28571428571428</v>
+      </c>
+      <c r="C10" s="3">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="D10" s="3">
+        <v>42.85714285714285</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>42.85714285714285</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.3603731907989429</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.176117145807734</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0.346834751788111</v>
+      </c>
+      <c r="K10" s="4">
+        <v>52.34985422740536</v>
+      </c>
+      <c r="L10" s="4">
+        <v>61.28571428571437</v>
+      </c>
+      <c r="M10" s="5">
+        <v>35</v>
+      </c>
+      <c r="N10" s="5">
+        <v>655343.8992500305</v>
+      </c>
+      <c r="O10" s="4">
+        <v>99.56607402765582</v>
+      </c>
+      <c r="P10" s="5">
+        <v>6582</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="C11" s="3">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="D11" s="3">
+        <v>54.28571428571428</v>
+      </c>
+      <c r="E11" s="3">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="F11" s="3">
+        <v>20</v>
+      </c>
+      <c r="G11" s="3">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="H11" s="4">
+        <v>5.939440356444176</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.5492699356334925</v>
+      </c>
+      <c r="J11" s="4">
+        <v>13.9768304804941</v>
+      </c>
+      <c r="K11" s="4">
+        <v>69.10981535471328</v>
+      </c>
+      <c r="L11" s="4">
+        <v>64.73505912432091</v>
+      </c>
+      <c r="M11" s="5">
+        <v>35</v>
+      </c>
+      <c r="N11" s="5">
+        <v>894328.9086818695</v>
+      </c>
+      <c r="O11" s="4">
+        <v>40.07747742244542</v>
+      </c>
+      <c r="P11" s="5">
+        <v>22315</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="C12" s="3">
+        <v>37.14285714285715</v>
+      </c>
+      <c r="D12" s="3">
+        <v>48.57142857142857</v>
+      </c>
+      <c r="E12" s="3">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="F12" s="3">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="G12" s="3">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="H12" s="4">
+        <v>3.521662805295045</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0.5151295148420868</v>
+      </c>
+      <c r="J12" s="4">
+        <v>8.034784464710153</v>
+      </c>
+      <c r="K12" s="4">
+        <v>67.60932944606402</v>
+      </c>
+      <c r="L12" s="4">
+        <v>61.7679769894532</v>
+      </c>
+      <c r="M12" s="5">
+        <v>35</v>
+      </c>
+      <c r="N12" s="5">
+        <v>256001.0578632355</v>
+      </c>
+      <c r="O12" s="4">
+        <v>18.55752503539221</v>
+      </c>
+      <c r="P12" s="5">
+        <v>13795</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="C13" s="3">
+        <v>40</v>
+      </c>
+      <c r="D13" s="3">
+        <v>45.71428571428572</v>
+      </c>
+      <c r="E13" s="3">
+        <v>25.71428571428571</v>
+      </c>
+      <c r="F13" s="3">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="G13" s="3">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="H13" s="4">
+        <v>3.907190234984487</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.155783922393409</v>
+      </c>
+      <c r="J13" s="4">
+        <v>11.01319533142003</v>
+      </c>
+      <c r="K13" s="4">
+        <v>59.56851311953344</v>
+      </c>
+      <c r="L13" s="4">
+        <v>59.1831255992331</v>
+      </c>
+      <c r="M13" s="5">
+        <v>35</v>
+      </c>
+      <c r="N13" s="5">
+        <v>2186658.451080322</v>
+      </c>
+      <c r="O13" s="4">
+        <v>74.77544886230285</v>
+      </c>
+      <c r="P13" s="5">
+        <v>29243</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="3">
+        <v>94.28571428571428</v>
+      </c>
+      <c r="C14" s="3">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0.1855728226369459</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.1641950408718832</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0.1814346965614235</v>
+      </c>
+      <c r="K14" s="4">
+        <v>88.63070942662772</v>
+      </c>
+      <c r="L14" s="4">
+        <v>90.35698306168331</v>
+      </c>
+      <c r="M14" s="5">
+        <v>35</v>
+      </c>
+      <c r="N14" s="5">
+        <v>818406.4252376556</v>
+      </c>
+      <c r="O14" s="4">
+        <v>236.6704526424684</v>
+      </c>
+      <c r="P14" s="5">
+        <v>3458</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="3">
+        <v>94.28571428571428</v>
+      </c>
+      <c r="C15" s="3">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="D15" s="3">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.134309957990946</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.1122216149800051</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0.09929131859617428</v>
+      </c>
+      <c r="K15" s="4">
+        <v>89.21574344023315</v>
+      </c>
+      <c r="L15" s="4">
+        <v>89.42345797379389</v>
+      </c>
+      <c r="M15" s="5">
+        <v>35</v>
+      </c>
+      <c r="N15" s="5">
+        <v>908292.0408248901</v>
+      </c>
+      <c r="O15" s="4">
+        <v>236.657644821493</v>
+      </c>
+      <c r="P15" s="5">
+        <v>3838</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="3">
+        <v>97.14285714285714</v>
+      </c>
+      <c r="C16" s="3">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0.1933391000830703</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.1686705494232735</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0.2005875057362257</v>
+      </c>
+      <c r="K16" s="4">
+        <v>88.89115646258502</v>
+      </c>
+      <c r="L16" s="4">
+        <v>90.07574304889981</v>
+      </c>
+      <c r="M16" s="5">
+        <v>35</v>
+      </c>
+      <c r="N16" s="5">
+        <v>329605.0052642822</v>
+      </c>
+      <c r="O16" s="4">
+        <v>97.37223198353979</v>
+      </c>
+      <c r="P16" s="5">
+        <v>3385</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="3">
+        <v>85.71428571428571</v>
+      </c>
+      <c r="C17" s="3">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="D17" s="3">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0.1609362270626764</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0.09348312325942437</v>
+      </c>
+      <c r="J17" s="4">
+        <v>0.2952937476748332</v>
+      </c>
+      <c r="K17" s="4">
+        <v>87.11467444120517</v>
+      </c>
+      <c r="L17" s="4">
+        <v>86.53723234260097</v>
+      </c>
+      <c r="M17" s="5">
+        <v>35</v>
+      </c>
+      <c r="N17" s="5">
+        <v>442256.3414573669</v>
+      </c>
+      <c r="O17" s="4">
+        <v>99.22735953721492</v>
+      </c>
+      <c r="P17" s="5">
+        <v>4457</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3868,10 +6474,10 @@
         <v>0</v>
       </c>
       <c r="K3" s="5">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="L3" s="5">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
@@ -3959,7 +6565,7 @@
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
@@ -4044,10 +6650,10 @@
         <v>0</v>
       </c>
       <c r="K7" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L7" s="5">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="M7" s="5">
         <v>0</v>
@@ -4220,10 +6826,10 @@
         <v>0</v>
       </c>
       <c r="K11" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L11" s="5">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="M11" s="5">
         <v>0</v>
@@ -4264,10 +6870,10 @@
         <v>0</v>
       </c>
       <c r="K12" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" s="5">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="M12" s="5">
         <v>0</v>
@@ -4308,10 +6914,10 @@
         <v>0</v>
       </c>
       <c r="K13" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L13" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M13" s="5">
         <v>0</v>
@@ -4509,9 +7115,764 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:N17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>6</v>
+      </c>
+      <c r="C3" s="5">
+        <v>11</v>
+      </c>
+      <c r="D3" s="5">
+        <v>18</v>
+      </c>
+      <c r="E3" s="5">
+        <v>5</v>
+      </c>
+      <c r="F3" s="5">
+        <v>13</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>5</v>
+      </c>
+      <c r="I3" s="5">
+        <v>5</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>4</v>
+      </c>
+      <c r="L3" s="5">
+        <v>10</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5">
+        <v>26</v>
+      </c>
+      <c r="C4" s="5">
+        <v>5</v>
+      </c>
+      <c r="D4" s="5">
+        <v>4</v>
+      </c>
+      <c r="E4" s="5">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5">
+        <v>4</v>
+      </c>
+      <c r="G4" s="5">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>4</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5">
+        <v>29</v>
+      </c>
+      <c r="C5" s="5">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5">
+        <v>6</v>
+      </c>
+      <c r="E5" s="5">
+        <v>1</v>
+      </c>
+      <c r="F5" s="5">
+        <v>3</v>
+      </c>
+      <c r="G5" s="5">
+        <v>2</v>
+      </c>
+      <c r="H5" s="5">
+        <v>1</v>
+      </c>
+      <c r="I5" s="5">
+        <v>1</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>3</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>18</v>
+      </c>
+      <c r="C6" s="5">
+        <v>5</v>
+      </c>
+      <c r="D6" s="5">
+        <v>12</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5">
+        <v>12</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>10</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>18</v>
+      </c>
+      <c r="C7" s="5">
+        <v>1</v>
+      </c>
+      <c r="D7" s="5">
+        <v>16</v>
+      </c>
+      <c r="E7" s="5">
+        <v>10</v>
+      </c>
+      <c r="F7" s="5">
+        <v>5</v>
+      </c>
+      <c r="G7" s="5">
+        <v>1</v>
+      </c>
+      <c r="H7" s="5">
+        <v>10</v>
+      </c>
+      <c r="I7" s="5">
+        <v>10</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>5</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>8</v>
+      </c>
+      <c r="C8" s="5">
+        <v>16</v>
+      </c>
+      <c r="D8" s="5">
+        <v>11</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5">
+        <v>9</v>
+      </c>
+      <c r="G8" s="5">
+        <v>2</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>2</v>
+      </c>
+      <c r="L8" s="5">
+        <v>8</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5">
+        <v>15</v>
+      </c>
+      <c r="C9" s="5">
+        <v>3</v>
+      </c>
+      <c r="D9" s="5">
+        <v>17</v>
+      </c>
+      <c r="E9" s="5">
+        <v>0</v>
+      </c>
+      <c r="F9" s="5">
+        <v>17</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5">
+        <v>0</v>
+      </c>
+      <c r="I9" s="5">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <v>16</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5">
+        <v>19</v>
+      </c>
+      <c r="C10" s="5">
+        <v>1</v>
+      </c>
+      <c r="D10" s="5">
+        <v>15</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5">
+        <v>15</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5">
+        <v>0</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <v>12</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5">
+        <v>10</v>
+      </c>
+      <c r="C11" s="5">
+        <v>6</v>
+      </c>
+      <c r="D11" s="5">
+        <v>19</v>
+      </c>
+      <c r="E11" s="5">
+        <v>10</v>
+      </c>
+      <c r="F11" s="5">
+        <v>7</v>
+      </c>
+      <c r="G11" s="5">
+        <v>2</v>
+      </c>
+      <c r="H11" s="5">
+        <v>10</v>
+      </c>
+      <c r="I11" s="5">
+        <v>10</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>7</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5">
+        <v>5</v>
+      </c>
+      <c r="C12" s="5">
+        <v>13</v>
+      </c>
+      <c r="D12" s="5">
+        <v>17</v>
+      </c>
+      <c r="E12" s="5">
+        <v>5</v>
+      </c>
+      <c r="F12" s="5">
+        <v>10</v>
+      </c>
+      <c r="G12" s="5">
+        <v>2</v>
+      </c>
+      <c r="H12" s="5">
+        <v>5</v>
+      </c>
+      <c r="I12" s="5">
+        <v>5</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>10</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="5">
+        <v>5</v>
+      </c>
+      <c r="C13" s="5">
+        <v>14</v>
+      </c>
+      <c r="D13" s="5">
+        <v>16</v>
+      </c>
+      <c r="E13" s="5">
+        <v>9</v>
+      </c>
+      <c r="F13" s="5">
+        <v>3</v>
+      </c>
+      <c r="G13" s="5">
+        <v>4</v>
+      </c>
+      <c r="H13" s="5">
+        <v>9</v>
+      </c>
+      <c r="I13" s="5">
+        <v>9</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5">
+        <v>1</v>
+      </c>
+      <c r="L13" s="5">
+        <v>2</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="5">
+        <v>33</v>
+      </c>
+      <c r="C14" s="5">
+        <v>0</v>
+      </c>
+      <c r="D14" s="5">
+        <v>2</v>
+      </c>
+      <c r="E14" s="5">
+        <v>0</v>
+      </c>
+      <c r="F14" s="5">
+        <v>2</v>
+      </c>
+      <c r="G14" s="5">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5">
+        <v>0</v>
+      </c>
+      <c r="J14" s="5">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5">
+        <v>2</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="5">
+        <v>33</v>
+      </c>
+      <c r="C15" s="5">
+        <v>1</v>
+      </c>
+      <c r="D15" s="5">
+        <v>1</v>
+      </c>
+      <c r="E15" s="5">
+        <v>0</v>
+      </c>
+      <c r="F15" s="5">
+        <v>1</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5">
+        <v>0</v>
+      </c>
+      <c r="I15" s="5">
+        <v>0</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5">
+        <v>1</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="5">
+        <v>34</v>
+      </c>
+      <c r="C16" s="5">
+        <v>0</v>
+      </c>
+      <c r="D16" s="5">
+        <v>1</v>
+      </c>
+      <c r="E16" s="5">
+        <v>0</v>
+      </c>
+      <c r="F16" s="5">
+        <v>1</v>
+      </c>
+      <c r="G16" s="5">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5">
+        <v>0</v>
+      </c>
+      <c r="I16" s="5">
+        <v>0</v>
+      </c>
+      <c r="J16" s="5">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <v>1</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="5">
+        <v>30</v>
+      </c>
+      <c r="C17" s="5">
+        <v>2</v>
+      </c>
+      <c r="D17" s="5">
+        <v>3</v>
+      </c>
+      <c r="E17" s="5">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5">
+        <v>3</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5">
+        <v>0</v>
+      </c>
+      <c r="I17" s="5">
+        <v>0</v>
+      </c>
+      <c r="J17" s="5">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5">
+        <v>3</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4522,9 +7883,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4558,8 +7925,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4581,25 +7956,41 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>5.609653797843334</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0</v>
-      </c>
+        <v>0.7368004627795166</v>
+      </c>
+      <c r="C3" s="4"/>
       <c r="D3" s="4">
-        <v>14.89457449028718</v>
+        <v>7.887785149284182</v>
       </c>
       <c r="E3" s="4">
-        <v>56.98129251700681</v>
+        <v>59.9744897959186</v>
       </c>
       <c r="F3" s="4">
-        <v>51.57718120805363</v>
+        <v>52.43428411633068</v>
       </c>
       <c r="G3" s="5">
         <v>8</v>
@@ -4608,113 +7999,153 @@
         <v>0</v>
       </c>
       <c r="I3" s="5">
+        <v>5</v>
+      </c>
+      <c r="J3" s="5">
         <v>3</v>
       </c>
-      <c r="J3" s="5">
-        <v>5</v>
-      </c>
       <c r="K3" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L3" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>0</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.7368004627795166</v>
+      </c>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="5">
+        <v>0</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.7368004627795166</v>
+        <v>1.265819855834404</v>
       </c>
       <c r="C4" s="4">
-        <v>0</v>
+        <v>0.526356687423789</v>
       </c>
       <c r="D4" s="4">
-        <v>7.887785149284182</v>
+        <v>6.4222870313475</v>
       </c>
       <c r="E4" s="4">
-        <v>59.9744897959186</v>
+        <v>64.95748299319726</v>
       </c>
       <c r="F4" s="4">
-        <v>52.43428411633068</v>
+        <v>57.90268456375843</v>
       </c>
       <c r="G4" s="5">
         <v>8</v>
       </c>
       <c r="H4" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I4" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J4" s="5">
+        <v>4</v>
+      </c>
+      <c r="K4" s="5">
+        <v>1</v>
+      </c>
+      <c r="L4" s="5">
         <v>3</v>
       </c>
-      <c r="K4" s="5">
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
         <v>2</v>
       </c>
-      <c r="L4" s="5">
-        <v>1</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="P4" s="4">
+        <v>1.265819855834404</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.526356687423789</v>
+      </c>
+      <c r="R4" s="5">
+        <v>2</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>1.265819855834404</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.526356687423789</v>
-      </c>
+        <v>5.609653797843334</v>
+      </c>
+      <c r="C5" s="4"/>
       <c r="D5" s="4">
-        <v>6.4222870313475</v>
+        <v>14.89457449028718</v>
       </c>
       <c r="E5" s="4">
-        <v>64.95748299319726</v>
+        <v>56.98129251700681</v>
       </c>
       <c r="F5" s="4">
-        <v>57.90268456375843</v>
+        <v>51.57718120805363</v>
       </c>
       <c r="G5" s="5">
         <v>8</v>
       </c>
       <c r="H5" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I5" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J5" s="5">
+        <v>5</v>
+      </c>
+      <c r="K5" s="5">
+        <v>1</v>
+      </c>
+      <c r="L5" s="5">
         <v>4</v>
       </c>
-      <c r="K5" s="5">
-        <v>1</v>
-      </c>
-      <c r="L5" s="5">
-        <v>3</v>
-      </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>0</v>
+      </c>
+      <c r="P5" s="4">
+        <v>5.609653797843334</v>
+      </c>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="5">
+        <v>0</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
         <v>5.791513389346918</v>
       </c>
-      <c r="C6" s="4">
-        <v>0</v>
-      </c>
+      <c r="C6" s="4"/>
       <c r="D6" s="4">
         <v>15.41138039628458</v>
       </c>
@@ -4745,10 +8176,24 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>0</v>
+      </c>
+      <c r="P6" s="4">
+        <v>5.791513389346918</v>
+      </c>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="5">
+        <v>0</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B7" s="4">
         <v>0.438781870980727</v>
@@ -4786,9 +8231,25 @@
       <c r="M7" s="5">
         <v>0</v>
       </c>
+      <c r="N7" s="4"/>
+      <c r="O7" s="5">
+        <v>4</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.438781870980727</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.4703072014777789</v>
+      </c>
+      <c r="R7" s="5">
+        <v>4</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4799,14 +8260,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4817,9 +8279,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4853,8 +8321,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4876,25 +8352,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>1.092224922873851</v>
+        <v>0.2975766827436864</v>
       </c>
       <c r="C3" s="4">
-        <v>1.286292130813862</v>
+        <v>0.263674603068</v>
       </c>
       <c r="D3" s="4">
-        <v>1.113499489524242</v>
+        <v>0.333906786617893</v>
       </c>
       <c r="E3" s="4">
-        <v>81.33928571428571</v>
+        <v>77.55102040816327</v>
       </c>
       <c r="F3" s="4">
-        <v>84.85738255033559</v>
+        <v>77.31963087248296</v>
       </c>
       <c r="G3" s="5">
         <v>8</v>
@@ -4903,39 +8397,57 @@
         <v>6</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.2072727534821488</v>
+      </c>
+      <c r="O3" s="5">
+        <v>6</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2528398280652489</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.20402546349675</v>
+      </c>
+      <c r="R3" s="5">
+        <v>6</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2975766827436864</v>
+        <v>0.4152394888994336</v>
       </c>
       <c r="C4" s="4">
-        <v>0.263674603068</v>
+        <v>0.5358908623888934</v>
       </c>
       <c r="D4" s="4">
-        <v>0.333906786617893</v>
+        <v>0.4362118559534375</v>
       </c>
       <c r="E4" s="4">
-        <v>77.55102040816327</v>
+        <v>78.68197278911568</v>
       </c>
       <c r="F4" s="4">
-        <v>77.31963087248296</v>
+        <v>80.38031319910512</v>
       </c>
       <c r="G4" s="5">
         <v>8</v>
@@ -4958,25 +8470,43 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.05581599655688804</v>
+      </c>
+      <c r="O4" s="5">
+        <v>6</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4291934880386556</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.5358908623888933</v>
+      </c>
+      <c r="R4" s="5">
+        <v>6</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.4152394888994336</v>
+        <v>1.092224922873851</v>
       </c>
       <c r="C5" s="4">
-        <v>0.5358908623888934</v>
+        <v>1.286292130813862</v>
       </c>
       <c r="D5" s="4">
-        <v>0.4362118559534375</v>
+        <v>1.113499489524242</v>
       </c>
       <c r="E5" s="4">
-        <v>78.68197278911568</v>
+        <v>81.33928571428571</v>
       </c>
       <c r="F5" s="4">
-        <v>80.38031319910512</v>
+        <v>84.85738255033559</v>
       </c>
       <c r="G5" s="5">
         <v>8</v>
@@ -4985,24 +8515,42 @@
         <v>6</v>
       </c>
       <c r="I5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4">
+        <v>1.286292130813862</v>
+      </c>
+      <c r="O5" s="5">
+        <v>6</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.4014013387567917</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2764455077557083</v>
+      </c>
+      <c r="R5" s="5">
+        <v>6</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
         <v>1.424126571414789</v>
@@ -5040,10 +8588,28 @@
       <c r="M6" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4">
+        <v>1.424126571414789</v>
+      </c>
+      <c r="O6" s="5">
+        <v>6</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.3112023353708204</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.3112023353708204</v>
+      </c>
+      <c r="R6" s="5">
+        <v>6</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B7" s="4">
         <v>0.24315332331227</v>
@@ -5081,9 +8647,25 @@
       <c r="M7" s="5">
         <v>0</v>
       </c>
+      <c r="N7" s="4"/>
+      <c r="O7" s="5">
+        <v>2</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.24315332331227</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.2903752545047062</v>
+      </c>
+      <c r="R7" s="5">
+        <v>2</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -5094,14 +8676,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -5112,9 +8695,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -5148,8 +8737,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -5171,122 +8768,176 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.7909986562140554</v>
+        <v>0.295869558905998</v>
       </c>
       <c r="C3" s="4">
-        <v>0.7422507120651293</v>
+        <v>0.1995524849857481</v>
       </c>
       <c r="D3" s="4">
-        <v>2.472137034782049</v>
+        <v>0.6213742232376726</v>
       </c>
       <c r="E3" s="4">
-        <v>82.2831632653061</v>
+        <v>78.34183673469387</v>
       </c>
       <c r="F3" s="4">
-        <v>81.33109619686797</v>
+        <v>76.79110738255048</v>
       </c>
       <c r="G3" s="5">
         <v>8</v>
       </c>
       <c r="H3" s="5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.1296480868631594</v>
+      </c>
+      <c r="O3" s="5">
+        <v>6</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.299383826329591</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.181094321118276</v>
+      </c>
+      <c r="R3" s="5">
+        <v>6</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.295869558905998</v>
+        <v>0.250053886777537</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1995524849857481</v>
+        <v>0.250053886777537</v>
       </c>
       <c r="D4" s="4">
-        <v>0.6213742232376726</v>
+        <v>0.3024133955299497</v>
       </c>
       <c r="E4" s="4">
-        <v>78.34183673469387</v>
+        <v>87.98469387755102</v>
       </c>
       <c r="F4" s="4">
-        <v>76.79110738255048</v>
+        <v>88.2005033557047</v>
       </c>
       <c r="G4" s="5">
         <v>8</v>
       </c>
       <c r="H4" s="5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.245530641908394</v>
+      </c>
+      <c r="O4" s="5">
+        <v>8</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1696788868815401</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1696788868815401</v>
+      </c>
+      <c r="R4" s="5">
+        <v>8</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.250053886777537</v>
+        <v>0.7909986562140554</v>
       </c>
       <c r="C5" s="4">
-        <v>0.250053886777537</v>
+        <v>0.7422507120651293</v>
       </c>
       <c r="D5" s="4">
-        <v>0.3024133955299497</v>
+        <v>2.472137034782049</v>
       </c>
       <c r="E5" s="4">
-        <v>87.98469387755102</v>
+        <v>82.2831632653061</v>
       </c>
       <c r="F5" s="4">
-        <v>88.2005033557047</v>
+        <v>81.33109619686797</v>
       </c>
       <c r="G5" s="5">
         <v>8</v>
       </c>
       <c r="H5" s="5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" s="5">
         <v>0</v>
@@ -5294,10 +8945,28 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4">
+        <v>0.7422507120651293</v>
+      </c>
+      <c r="O5" s="5">
+        <v>7</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1882895261806924</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1594760937505901</v>
+      </c>
+      <c r="R5" s="5">
+        <v>7</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
         <v>2.556996927656651</v>
@@ -5335,10 +9004,28 @@
       <c r="M6" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4">
+        <v>2.699110694473406</v>
+      </c>
+      <c r="O6" s="5">
+        <v>5</v>
+      </c>
+      <c r="P6" s="4">
+        <v>2.36196978431513</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>1.46151626795955</v>
+      </c>
+      <c r="R6" s="5">
+        <v>3</v>
+      </c>
+      <c r="S6" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B7" s="4">
         <v>0.312290228982436</v>
@@ -5376,9 +9063,27 @@
       <c r="M7" s="5">
         <v>0</v>
       </c>
+      <c r="N7" s="4">
+        <v>-0.312290228982436</v>
+      </c>
+      <c r="O7" s="5">
+        <v>5</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.09740583936886088</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.09740583936886088</v>
+      </c>
+      <c r="R7" s="5">
+        <v>5</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -5389,14 +9094,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -5407,9 +9113,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -5443,8 +9155,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -5466,66 +9186,100 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.7868297965310781</v>
+        <v>0.2542219229087657</v>
       </c>
       <c r="C3" s="4">
-        <v>0.6683149253870521</v>
+        <v>0.2215711899815899</v>
       </c>
       <c r="D3" s="4">
-        <v>1.157565918662426</v>
+        <v>0.5189072058573272</v>
       </c>
       <c r="E3" s="4">
-        <v>81.56887755102041</v>
+        <v>75.4294217687075</v>
       </c>
       <c r="F3" s="4">
-        <v>84.19183445190156</v>
+        <v>73.74999999999989</v>
       </c>
       <c r="G3" s="5">
         <v>8</v>
       </c>
       <c r="H3" s="5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>4</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2542219229087657</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2215711899815899</v>
+      </c>
+      <c r="R3" s="5">
+        <v>4</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2542219229087657</v>
+        <v>0.4680777274622119</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2215711899815899</v>
+        <v>0.4813549545490527</v>
       </c>
       <c r="D4" s="4">
-        <v>0.5189072058573272</v>
+        <v>0.6543846808923877</v>
       </c>
       <c r="E4" s="4">
-        <v>75.4294217687075</v>
+        <v>79.88945578231292</v>
       </c>
       <c r="F4" s="4">
-        <v>73.74999999999989</v>
+        <v>79.22119686800897</v>
       </c>
       <c r="G4" s="5">
         <v>8</v>
@@ -5534,48 +9288,64 @@
         <v>4</v>
       </c>
       <c r="I4" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J4" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>4</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4680777274622119</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.4813549545490527</v>
+      </c>
+      <c r="R4" s="5">
+        <v>4</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.4680777274622119</v>
+        <v>0.7868297965310781</v>
       </c>
       <c r="C5" s="4">
-        <v>0.4813549545490527</v>
+        <v>0.6683149253870521</v>
       </c>
       <c r="D5" s="4">
-        <v>0.6543846808923877</v>
+        <v>1.157565918662426</v>
       </c>
       <c r="E5" s="4">
-        <v>79.88945578231292</v>
+        <v>81.56887755102041</v>
       </c>
       <c r="F5" s="4">
-        <v>79.22119686800897</v>
+        <v>84.19183445190156</v>
       </c>
       <c r="G5" s="5">
         <v>8</v>
       </c>
       <c r="H5" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I5" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J5" s="5">
         <v>2</v>
@@ -5589,10 +9359,28 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4">
+        <v>0.6683149253870521</v>
+      </c>
+      <c r="O5" s="5">
+        <v>6</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.44413851224025</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.4068160288156563</v>
+      </c>
+      <c r="R5" s="5">
+        <v>6</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
         <v>1.161667452253819</v>
@@ -5630,10 +9418,26 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>2</v>
+      </c>
+      <c r="P6" s="4">
+        <v>1.161667452253819</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.8894141836827307</v>
+      </c>
+      <c r="R6" s="5">
+        <v>2</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B7" s="4">
         <v>0.2521446691394972</v>
@@ -5671,9 +9475,25 @@
       <c r="M7" s="5">
         <v>0</v>
       </c>
+      <c r="N7" s="4"/>
+      <c r="O7" s="5">
+        <v>2</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.2521446691394972</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.2521248369321953</v>
+      </c>
+      <c r="R7" s="5">
+        <v>2</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -5684,14 +9504,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -5702,9 +9523,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -5738,8 +9565,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -5761,25 +9596,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>2.394363251426098</v>
+        <v>1.301017962189648</v>
       </c>
       <c r="C3" s="4">
-        <v>0.6525069641720274</v>
+        <v>0.1851062019279238</v>
       </c>
       <c r="D3" s="4">
-        <v>9.264454212882397</v>
+        <v>6.681586824151012</v>
       </c>
       <c r="E3" s="4">
-        <v>71.17346938775474</v>
+        <v>72.94642857142857</v>
       </c>
       <c r="F3" s="4">
-        <v>72.62444071588253</v>
+        <v>70.79278523489891</v>
       </c>
       <c r="G3" s="5">
         <v>8</v>
@@ -5794,100 +9647,148 @@
         <v>4</v>
       </c>
       <c r="K3" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L3" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>4</v>
+      </c>
+      <c r="P3" s="4">
+        <v>1.301017962189648</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1851062019279238</v>
+      </c>
+      <c r="R3" s="5">
+        <v>4</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>1.301017962189648</v>
+        <v>1.270161200758164</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1851062019279238</v>
+        <v>0.03975516013434897</v>
       </c>
       <c r="D4" s="4">
-        <v>6.681586824151012</v>
+        <v>5.181359816785997</v>
       </c>
       <c r="E4" s="4">
-        <v>72.94642857142857</v>
+        <v>74.29846938775511</v>
       </c>
       <c r="F4" s="4">
-        <v>70.79278523489891</v>
+        <v>72.68736017897091</v>
       </c>
       <c r="G4" s="5">
         <v>8</v>
       </c>
       <c r="H4" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="5">
         <v>4</v>
       </c>
       <c r="K4" s="5">
+        <v>1</v>
+      </c>
+      <c r="L4" s="5">
+        <v>2</v>
+      </c>
+      <c r="M4" s="5">
+        <v>1</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
         <v>4</v>
       </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="P4" s="4">
+        <v>1.270161200758164</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.03975516013434897</v>
+      </c>
+      <c r="R4" s="5">
+        <v>3</v>
+      </c>
+      <c r="S4" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>1.270161200758164</v>
+        <v>2.394363251426098</v>
       </c>
       <c r="C5" s="4">
-        <v>0.03975516013434897</v>
+        <v>0.6525069641720274</v>
       </c>
       <c r="D5" s="4">
-        <v>5.181359816785997</v>
+        <v>9.264454212882397</v>
       </c>
       <c r="E5" s="4">
-        <v>74.29846938775511</v>
+        <v>71.17346938775474</v>
       </c>
       <c r="F5" s="4">
-        <v>72.68736017897091</v>
+        <v>72.62444071588253</v>
       </c>
       <c r="G5" s="5">
         <v>8</v>
       </c>
       <c r="H5" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" s="5">
         <v>4</v>
       </c>
       <c r="K5" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L5" s="5">
         <v>2</v>
       </c>
       <c r="M5" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>4</v>
+      </c>
+      <c r="P5" s="4">
+        <v>2.394363251426098</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.6525069641720274</v>
+      </c>
+      <c r="R5" s="5">
+        <v>4</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
         <v>6.041564569868565</v>
@@ -5925,10 +9826,26 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>2</v>
+      </c>
+      <c r="P6" s="4">
+        <v>6.041564569868565</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>1.153967636035422</v>
+      </c>
+      <c r="R6" s="5">
+        <v>2</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B7" s="4">
         <v>0.3110780824750278</v>
@@ -5966,9 +9883,27 @@
       <c r="M7" s="5">
         <v>0</v>
       </c>
+      <c r="N7" s="4">
+        <v>-0.2732386962370747</v>
+      </c>
+      <c r="O7" s="5">
+        <v>5</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.162592328092926</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.162592328092926</v>
+      </c>
+      <c r="R7" s="5">
+        <v>5</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -5979,596 +9914,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>3.615707080292309</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0</v>
-      </c>
-      <c r="D3" s="4">
-        <v>7.57648836458444</v>
-      </c>
-      <c r="E3" s="4">
-        <v>61.98129251700681</v>
-      </c>
-      <c r="F3" s="4">
-        <v>53.66051454138711</v>
-      </c>
-      <c r="G3" s="5">
-        <v>8</v>
-      </c>
-      <c r="H3" s="5">
-        <v>0</v>
-      </c>
-      <c r="I3" s="5">
-        <v>5</v>
-      </c>
-      <c r="J3" s="5">
-        <v>3</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>2</v>
-      </c>
-      <c r="M3" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>1.218089500220623</v>
-      </c>
-      <c r="C4" s="4">
-        <v>1.02192026862908</v>
-      </c>
-      <c r="D4" s="4">
-        <v>4.714902292009376</v>
-      </c>
-      <c r="E4" s="4">
-        <v>68.94132653061224</v>
-      </c>
-      <c r="F4" s="4">
-        <v>55.69630872483221</v>
-      </c>
-      <c r="G4" s="5">
-        <v>8</v>
-      </c>
-      <c r="H4" s="5">
-        <v>1</v>
-      </c>
-      <c r="I4" s="5">
-        <v>6</v>
-      </c>
-      <c r="J4" s="5">
-        <v>1</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>1</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>1.262178020419262</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.9060182164165722</v>
-      </c>
-      <c r="D5" s="4">
-        <v>3.355189646543077</v>
-      </c>
-      <c r="E5" s="4">
-        <v>68.58418367346938</v>
-      </c>
-      <c r="F5" s="4">
-        <v>56.84563758389262</v>
-      </c>
-      <c r="G5" s="5">
-        <v>8</v>
-      </c>
-      <c r="H5" s="5">
-        <v>2</v>
-      </c>
-      <c r="I5" s="5">
-        <v>5</v>
-      </c>
-      <c r="J5" s="5">
-        <v>1</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>1</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B6" s="4">
-        <v>4.418034630689792</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0</v>
-      </c>
-      <c r="D6" s="4">
-        <v>8.710875297601712</v>
-      </c>
-      <c r="E6" s="4">
-        <v>58.82653061224453</v>
-      </c>
-      <c r="F6" s="4">
-        <v>54.82102908277395</v>
-      </c>
-      <c r="G6" s="5">
-        <v>6</v>
-      </c>
-      <c r="H6" s="5">
-        <v>0</v>
-      </c>
-      <c r="I6" s="5">
-        <v>0</v>
-      </c>
-      <c r="J6" s="5">
-        <v>6</v>
-      </c>
-      <c r="K6" s="5">
-        <v>0</v>
-      </c>
-      <c r="L6" s="5">
-        <v>5</v>
-      </c>
-      <c r="M6" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
-      <c r="A7" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B7" s="4">
-        <v>0.2238663620238519</v>
-      </c>
-      <c r="C7" s="4">
-        <v>0.2238663620238519</v>
-      </c>
-      <c r="D7" s="4">
-        <v>0.2653326361232615</v>
-      </c>
-      <c r="E7" s="4">
-        <v>86.57142857142857</v>
-      </c>
-      <c r="F7" s="4">
-        <v>88.67785234899328</v>
-      </c>
-      <c r="G7" s="5">
-        <v>5</v>
-      </c>
-      <c r="H7" s="5">
-        <v>5</v>
-      </c>
-      <c r="I7" s="5">
-        <v>0</v>
-      </c>
-      <c r="J7" s="5">
-        <v>0</v>
-      </c>
-      <c r="K7" s="5">
-        <v>0</v>
-      </c>
-      <c r="L7" s="5">
-        <v>0</v>
-      </c>
-      <c r="M7" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>1.681096878745434</v>
-      </c>
-      <c r="C3" s="4">
-        <v>1.466332825573694</v>
-      </c>
-      <c r="D3" s="4">
-        <v>2.085915413596508</v>
-      </c>
-      <c r="E3" s="4">
-        <v>64.26870748299307</v>
-      </c>
-      <c r="F3" s="4">
-        <v>66.91694630872432</v>
-      </c>
-      <c r="G3" s="5">
-        <v>8</v>
-      </c>
-      <c r="H3" s="5">
-        <v>5</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>3</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>3</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.281843700340459</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.2267154500439453</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.8192100905687304</v>
-      </c>
-      <c r="E4" s="4">
-        <v>60.82057823129251</v>
-      </c>
-      <c r="F4" s="4">
-        <v>61.84144295302013</v>
-      </c>
-      <c r="G4" s="5">
-        <v>8</v>
-      </c>
-      <c r="H4" s="5">
-        <v>4</v>
-      </c>
-      <c r="I4" s="5">
-        <v>1</v>
-      </c>
-      <c r="J4" s="5">
-        <v>3</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>3</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.8366957389368213</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.7545632904838184</v>
-      </c>
-      <c r="D5" s="4">
-        <v>1.003677412206875</v>
-      </c>
-      <c r="E5" s="4">
-        <v>68.41836734693878</v>
-      </c>
-      <c r="F5" s="4">
-        <v>70.50055928411632</v>
-      </c>
-      <c r="G5" s="5">
-        <v>8</v>
-      </c>
-      <c r="H5" s="5">
-        <v>4</v>
-      </c>
-      <c r="I5" s="5">
-        <v>1</v>
-      </c>
-      <c r="J5" s="5">
-        <v>3</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>3</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B6" s="4">
-        <v>2.283423370120844</v>
-      </c>
-      <c r="C6" s="4">
-        <v>1.84475266177111</v>
-      </c>
-      <c r="D6" s="4">
-        <v>2.737409855919997</v>
-      </c>
-      <c r="E6" s="4">
-        <v>60.45918367346934</v>
-      </c>
-      <c r="F6" s="4">
-        <v>62.01715137956734</v>
-      </c>
-      <c r="G6" s="5">
-        <v>6</v>
-      </c>
-      <c r="H6" s="5">
-        <v>2</v>
-      </c>
-      <c r="I6" s="5">
-        <v>1</v>
-      </c>
-      <c r="J6" s="5">
-        <v>3</v>
-      </c>
-      <c r="K6" s="5">
-        <v>0</v>
-      </c>
-      <c r="L6" s="5">
-        <v>3</v>
-      </c>
-      <c r="M6" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
-      <c r="A7" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B7" s="4">
-        <v>0.5522014037566059</v>
-      </c>
-      <c r="C7" s="4">
-        <v>0</v>
-      </c>
-      <c r="D7" s="4">
-        <v>0.6244008554576708</v>
-      </c>
-      <c r="E7" s="4">
-        <v>53.6530612244898</v>
-      </c>
-      <c r="F7" s="4">
-        <v>48.48322147651007</v>
-      </c>
-      <c r="G7" s="5">
-        <v>5</v>
-      </c>
-      <c r="H7" s="5">
-        <v>0</v>
-      </c>
-      <c r="I7" s="5">
-        <v>0</v>
-      </c>
-      <c r="J7" s="5">
-        <v>5</v>
-      </c>
-      <c r="K7" s="5">
-        <v>0</v>
-      </c>
-      <c r="L7" s="5">
-        <v>5</v>
-      </c>
-      <c r="M7" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/downloads/mgfieldslanders2018.xlsx
+++ b/public/downloads/mgfieldslanders2018.xlsx
@@ -1783,16 +1783,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.2238663620238519</v>
+        <v>-0.1198154316587529</v>
       </c>
       <c r="O7" s="5">
         <v>5</v>
       </c>
       <c r="P7" s="4">
-        <v>0.1736692103147292</v>
+        <v>0.1528590242417094</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1736692103147292</v>
+        <v>0.1528590242417094</v>
       </c>
       <c r="R7" s="5">
         <v>5</v>
@@ -2079,16 +2079,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>1.466332825573694</v>
+        <v>1.56379126313527</v>
       </c>
       <c r="O5" s="5">
         <v>5</v>
       </c>
       <c r="P5" s="4">
-        <v>0.5274361210362141</v>
+        <v>0.5030715116458203</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.33973706038509</v>
+        <v>0.320245372872775</v>
       </c>
       <c r="R5" s="5">
         <v>5</v>
@@ -2371,7 +2371,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.04844509037226263</v>
+        <v>-0.02590504615826328</v>
       </c>
       <c r="O3" s="5">
         <v>5</v>
@@ -2380,7 +2380,7 @@
         <v>0.3471930390528728</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1477739198437487</v>
+        <v>0.1329038925376436</v>
       </c>
       <c r="R3" s="5">
         <v>5</v>
@@ -2430,16 +2430,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.0833285650383371</v>
+        <v>-0.09677343483524026</v>
       </c>
       <c r="O4" s="5">
         <v>5</v>
       </c>
       <c r="P4" s="4">
-        <v>0.295631082677642</v>
+        <v>0.2989923001268678</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.08065482228200971</v>
+        <v>0.07796584832262908</v>
       </c>
       <c r="R4" s="5">
         <v>5</v>
@@ -2840,16 +2840,16 @@
         <v>2</v>
       </c>
       <c r="N4" s="4">
-        <v>2.251121085974801</v>
+        <v>1.282379851451426</v>
       </c>
       <c r="O4" s="5">
         <v>5</v>
       </c>
       <c r="P4" s="4">
-        <v>3.401776238621899</v>
+        <v>3.167961253393399</v>
       </c>
       <c r="Q4" s="4">
-        <v>1.361709744709979</v>
+        <v>0.54326639985375</v>
       </c>
       <c r="R4" s="5">
         <v>3</v>
@@ -3005,16 +3005,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.2488572493986957</v>
+        <v>-0.2340622874529883</v>
       </c>
       <c r="O7" s="5">
         <v>5</v>
       </c>
       <c r="P7" s="4">
-        <v>0.125298696245624</v>
+        <v>0.1223397038564825</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.125298696245624</v>
+        <v>0.1223397038564825</v>
       </c>
       <c r="R7" s="5">
         <v>5</v>
@@ -3795,16 +3795,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.1196320907072895</v>
+        <v>-0.06288601511233205</v>
       </c>
       <c r="O7" s="5">
         <v>5</v>
       </c>
       <c r="P7" s="4">
-        <v>0.155783922393409</v>
+        <v>0.1444347072744175</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.155783922393409</v>
+        <v>0.1444347072744175</v>
       </c>
       <c r="R7" s="5">
         <v>5</v>
@@ -3977,16 +3977,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.03158541790023504</v>
+        <v>0.1608598772404544</v>
       </c>
       <c r="O3" s="5">
         <v>7</v>
       </c>
       <c r="P3" s="4">
-        <v>0.297750983190549</v>
+        <v>0.279797096180872</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2011320900420285</v>
+        <v>0.1621455821252233</v>
       </c>
       <c r="R3" s="5">
         <v>7</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.05163051121924545</v>
+        <v>0.1210153021927193</v>
       </c>
       <c r="O4" s="5">
         <v>8</v>
       </c>
       <c r="P4" s="4">
-        <v>0.142060779132386</v>
+        <v>0.1268595156609498</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.142060779132386</v>
+        <v>0.1268595156609498</v>
       </c>
       <c r="R4" s="5">
         <v>8</v>
@@ -4095,7 +4095,7 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.1841122212775715</v>
+        <v>0.20360863162207</v>
       </c>
       <c r="O5" s="5">
         <v>7</v>
@@ -4104,7 +4104,7 @@
         <v>0.05217117023802196</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.04497716480191564</v>
+        <v>0.04219196332413015</v>
       </c>
       <c r="R5" s="5">
         <v>7</v>
@@ -4154,16 +4154,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>0.1080399215200778</v>
+        <v>0.1775717320543501</v>
       </c>
       <c r="O6" s="5">
         <v>6</v>
       </c>
       <c r="P6" s="4">
-        <v>0.1776956906854402</v>
+        <v>0.1615895627371755</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.1776956906854402</v>
+        <v>0.1615895627371755</v>
       </c>
       <c r="R6" s="5">
         <v>6</v>
@@ -4213,16 +4213,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.3341589347319477</v>
+        <v>-0.2259014281065985</v>
       </c>
       <c r="O7" s="5">
         <v>5</v>
       </c>
       <c r="P7" s="4">
-        <v>0.2986022375385617</v>
+        <v>0.2769507362134919</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.2986022375385617</v>
+        <v>0.2769507362134919</v>
       </c>
       <c r="R7" s="5">
         <v>5</v>
@@ -4395,16 +4395,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.6355511842034739</v>
+        <v>-0.6686431273974671</v>
       </c>
       <c r="O3" s="5">
         <v>7</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1877752162754068</v>
+        <v>0.1783158196165497</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.08699762130430232</v>
+        <v>0.0809143027218933</v>
       </c>
       <c r="R3" s="5">
         <v>7</v>
@@ -4454,16 +4454,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.3857773055410108</v>
+        <v>-0.4008203764678133</v>
       </c>
       <c r="O4" s="5">
         <v>8</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1180431993181073</v>
+        <v>0.1156038600764774</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1180431993181073</v>
+        <v>0.1156038600764774</v>
       </c>
       <c r="R4" s="5">
         <v>8</v>
@@ -4513,16 +4513,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.3574024363634948</v>
+        <v>-0.4484474395064298</v>
       </c>
       <c r="O5" s="5">
         <v>7</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1157885271234613</v>
+        <v>0.09302727633772753</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1174273375311269</v>
+        <v>0.1044209085107076</v>
       </c>
       <c r="R5" s="5">
         <v>7</v>
@@ -4572,16 +4572,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.08978840112892846</v>
+        <v>-0.1071782112067992</v>
       </c>
       <c r="O6" s="5">
         <v>6</v>
       </c>
       <c r="P6" s="4">
-        <v>0.05721801140843077</v>
+        <v>0.0522508473265843</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.05721801140843077</v>
+        <v>0.0522508473265843</v>
       </c>
       <c r="R6" s="5">
         <v>6</v>
@@ -4631,16 +4631,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.5569618359999445</v>
+        <v>-0.5525230201514288</v>
       </c>
       <c r="O7" s="5">
         <v>5</v>
       </c>
       <c r="P7" s="4">
-        <v>0.1969369838993445</v>
+        <v>0.1960492207296413</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1969369838993445</v>
+        <v>0.1960492207296413</v>
       </c>
       <c r="R7" s="5">
         <v>5</v>
@@ -4813,16 +4813,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.06832744947448431</v>
+        <v>0.1724527296607655</v>
       </c>
       <c r="O3" s="5">
         <v>7</v>
       </c>
       <c r="P3" s="4">
-        <v>0.311969160836944</v>
+        <v>0.3105781268357757</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2090976377399132</v>
+        <v>0.1926328445691091</v>
       </c>
       <c r="R3" s="5">
         <v>7</v>
@@ -4872,7 +4872,7 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.06716868215297245</v>
+        <v>0.09919961908938391</v>
       </c>
       <c r="O4" s="5">
         <v>8</v>
@@ -4931,16 +4931,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.2263585859023462</v>
+        <v>0.1863094857891371</v>
       </c>
       <c r="O5" s="5">
         <v>8</v>
       </c>
       <c r="P5" s="4">
-        <v>0.08870634794495376</v>
+        <v>0.08187149957887876</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.08870634794495376</v>
+        <v>0.08187149957887876</v>
       </c>
       <c r="R5" s="5">
         <v>8</v>
@@ -4990,16 +4990,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>0.1633263289907809</v>
+        <v>0.2839025887352201</v>
       </c>
       <c r="O6" s="5">
         <v>6</v>
       </c>
       <c r="P6" s="4">
-        <v>0.1960584015587261</v>
+        <v>0.1628310086095801</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.1960584015587261</v>
+        <v>0.1628310086095801</v>
       </c>
       <c r="R6" s="5">
         <v>6</v>
@@ -5049,16 +5049,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.2867686823801812</v>
+        <v>-0.2489798697264716</v>
       </c>
       <c r="O7" s="5">
         <v>5</v>
       </c>
       <c r="P7" s="4">
-        <v>0.2656385324757</v>
+        <v>0.2580807699449582</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.2656385324757</v>
+        <v>0.2580807699449582</v>
       </c>
       <c r="R7" s="5">
         <v>5</v>
@@ -5231,16 +5231,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.306642234688076</v>
+        <v>-0.2798580230366358</v>
       </c>
       <c r="O3" s="5">
         <v>6</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2154763496946655</v>
+        <v>0.2177099318041032</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.07492502363018975</v>
+        <v>0.06897506255895997</v>
       </c>
       <c r="R3" s="5">
         <v>6</v>
@@ -5290,16 +5290,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.2516801771862278</v>
+        <v>-0.2673639492234103</v>
       </c>
       <c r="O4" s="5">
         <v>7</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1157612938081304</v>
+        <v>0.1142064971069038</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.07963346259396596</v>
+        <v>0.07561601321582383</v>
       </c>
       <c r="R4" s="5">
         <v>7</v>
@@ -5349,16 +5349,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.101802378617934</v>
+        <v>-0.0875346225691796</v>
       </c>
       <c r="O5" s="5">
         <v>7</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2050234273677824</v>
+        <v>0.1994830984398943</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.08376202865906904</v>
+        <v>0.07946847503416185</v>
       </c>
       <c r="R5" s="5">
         <v>7</v>
@@ -5408,16 +5408,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>0.07105264241041219</v>
+        <v>0.1067504758175776</v>
       </c>
       <c r="O6" s="5">
         <v>5</v>
       </c>
       <c r="P6" s="4">
-        <v>0.06760808223992128</v>
+        <v>0.05570880443753282</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.05482884608816564</v>
+        <v>0.04768927940673257</v>
       </c>
       <c r="R6" s="5">
         <v>5</v>
@@ -5467,16 +5467,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.4879506246046922</v>
+        <v>-0.4511677356989905</v>
       </c>
       <c r="O7" s="5">
         <v>5</v>
       </c>
       <c r="P7" s="4">
-        <v>0.1874061773579039</v>
+        <v>0.1800495995767635</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1874061773579039</v>
+        <v>0.1800495995767635</v>
       </c>
       <c r="R7" s="5">
         <v>5</v>
@@ -5663,13 +5663,13 @@
         <v>0</v>
       </c>
       <c r="H4" s="4">
-        <v>0.3357273676477669</v>
+        <v>0.3366810723465307</v>
       </c>
       <c r="I4" s="4">
         <v>0.3286975201185556</v>
       </c>
       <c r="J4" s="4">
-        <v>0.3406785833467037</v>
+        <v>0.3376789637083818</v>
       </c>
       <c r="K4" s="4">
         <v>78.41982507288624</v>
@@ -5695,13 +5695,13 @@
         <v>19</v>
       </c>
       <c r="B5" s="3">
-        <v>82.85714285714286</v>
+        <v>85.71428571428571</v>
       </c>
       <c r="C5" s="3">
         <v>0</v>
       </c>
       <c r="D5" s="3">
-        <v>17.14285714285714</v>
+        <v>14.28571428571428</v>
       </c>
       <c r="E5" s="3">
         <v>2.857142857142857</v>
@@ -5710,16 +5710,16 @@
         <v>8.571428571428571</v>
       </c>
       <c r="G5" s="3">
-        <v>5.714285714285714</v>
+        <v>2.857142857142857</v>
       </c>
       <c r="H5" s="4">
-        <v>0.5690761662248479</v>
+        <v>0.4676071097682329</v>
       </c>
       <c r="I5" s="4">
-        <v>0.2907554371978988</v>
+        <v>0.1834489063734809</v>
       </c>
       <c r="J5" s="4">
-        <v>1.150419670920619</v>
+        <v>1.193826193048698</v>
       </c>
       <c r="K5" s="4">
         <v>82.68804664723042</v>
@@ -5769,7 +5769,7 @@
         <v>0.4186488217914645</v>
       </c>
       <c r="J6" s="4">
-        <v>0.7806597827537098</v>
+        <v>0.7800081532294754</v>
       </c>
       <c r="K6" s="4">
         <v>76.75024295432452</v>
@@ -5813,13 +5813,13 @@
         <v>2.857142857142857</v>
       </c>
       <c r="H7" s="4">
-        <v>2.193905382133351</v>
+        <v>2.193753405739166</v>
       </c>
       <c r="I7" s="4">
-        <v>0.3661452809632403</v>
+        <v>0.3658497713078803</v>
       </c>
       <c r="J7" s="4">
-        <v>7.02330177644058</v>
+        <v>7.022845847258024</v>
       </c>
       <c r="K7" s="4">
         <v>74.16520894071911</v>
@@ -5863,13 +5863,13 @@
         <v>5.714285714285714</v>
       </c>
       <c r="H8" s="4">
-        <v>2.175552875519142</v>
+        <v>2.172579991794424</v>
       </c>
       <c r="I8" s="4">
-        <v>0.4627878441294838</v>
+        <v>0.4497814778338465</v>
       </c>
       <c r="J8" s="4">
-        <v>5.095670986603451</v>
+        <v>5.097288888467013</v>
       </c>
       <c r="K8" s="4">
         <v>68.05344995140923</v>
@@ -5913,13 +5913,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="4">
-        <v>0.8465529063433157</v>
+        <v>0.8409838527683685</v>
       </c>
       <c r="I9" s="4">
-        <v>0.620887039171915</v>
+        <v>0.6143898100011432</v>
       </c>
       <c r="J9" s="4">
-        <v>1.160357923107193</v>
+        <v>1.154232592326481</v>
       </c>
       <c r="K9" s="4">
         <v>62.25947521865874</v>
@@ -5963,13 +5963,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <v>0.3603731907989429</v>
+        <v>0.3611414690730516</v>
       </c>
       <c r="I10" s="4">
-        <v>0.176117145807734</v>
+        <v>0.1714963560010272</v>
       </c>
       <c r="J10" s="4">
-        <v>0.346834751788111</v>
+        <v>0.3524277566576665</v>
       </c>
       <c r="K10" s="4">
         <v>52.34985422740536</v>
@@ -6013,13 +6013,13 @@
         <v>5.714285714285714</v>
       </c>
       <c r="H11" s="4">
-        <v>5.939440356444176</v>
+        <v>5.885574218050641</v>
       </c>
       <c r="I11" s="4">
-        <v>0.5492699356334925</v>
+        <v>0.302257435982053</v>
       </c>
       <c r="J11" s="4">
-        <v>13.9768304804941</v>
+        <v>14.11699511770373</v>
       </c>
       <c r="K11" s="4">
         <v>69.10981535471328</v>
@@ -6113,13 +6113,13 @@
         <v>11.42857142857143</v>
       </c>
       <c r="H13" s="4">
-        <v>3.907190234984487</v>
+        <v>3.905568918538918</v>
       </c>
       <c r="I13" s="4">
-        <v>0.155783922393409</v>
+        <v>0.1444347072744175</v>
       </c>
       <c r="J13" s="4">
-        <v>11.01319533142003</v>
+        <v>11.01157401497446</v>
       </c>
       <c r="K13" s="4">
         <v>59.56851311953344</v>
@@ -6163,13 +6163,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="4">
-        <v>0.1855728226369459</v>
+        <v>0.1721403804036932</v>
       </c>
       <c r="I14" s="4">
-        <v>0.1641950408718832</v>
+        <v>0.1454403030582904</v>
       </c>
       <c r="J14" s="4">
-        <v>0.1814346965614235</v>
+        <v>0.174487639249404</v>
       </c>
       <c r="K14" s="4">
         <v>88.63070942662772</v>
@@ -6213,13 +6213,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <v>0.134309957990946</v>
+        <v>0.12540933816725</v>
       </c>
       <c r="I15" s="4">
-        <v>0.1122216149800051</v>
+        <v>0.1065432892984163</v>
       </c>
       <c r="J15" s="4">
-        <v>0.09929131859617428</v>
+        <v>0.1035253647570366</v>
       </c>
       <c r="K15" s="4">
         <v>89.21574344023315</v>
@@ -6263,13 +6263,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="4">
-        <v>0.1933391000830703</v>
+        <v>0.1846830935320264</v>
       </c>
       <c r="I16" s="4">
-        <v>0.1686705494232735</v>
+        <v>0.1566974462034849</v>
       </c>
       <c r="J16" s="4">
-        <v>0.2005875057362257</v>
+        <v>0.1937941437290844</v>
       </c>
       <c r="K16" s="4">
         <v>88.89115646258502</v>
@@ -6313,13 +6313,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="4">
-        <v>0.1609362270626764</v>
+        <v>0.1567342012376065</v>
       </c>
       <c r="I17" s="4">
-        <v>0.09348312325942437</v>
+        <v>0.08793787293403801</v>
       </c>
       <c r="J17" s="4">
-        <v>0.2952937476748332</v>
+        <v>0.2909083125945983</v>
       </c>
       <c r="K17" s="4">
         <v>87.11467444120517</v>
@@ -7290,13 +7290,13 @@
         <v>19</v>
       </c>
       <c r="B5" s="5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C5" s="5">
         <v>0</v>
       </c>
       <c r="D5" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E5" s="5">
         <v>1</v>
@@ -7305,7 +7305,7 @@
         <v>3</v>
       </c>
       <c r="G5" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H5" s="5">
         <v>1</v>
@@ -8412,7 +8412,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2072727534821488</v>
+        <v>-0.21055704885475</v>
       </c>
       <c r="O3" s="5">
         <v>6</v>
@@ -8471,13 +8471,13 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.05581599655688804</v>
+        <v>0.1124008802886719</v>
       </c>
       <c r="O4" s="5">
         <v>6</v>
       </c>
       <c r="P4" s="4">
-        <v>0.4291934880386556</v>
+        <v>0.4433397089716016</v>
       </c>
       <c r="Q4" s="4">
         <v>0.5358908623888933</v>
@@ -8530,13 +8530,13 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>1.286292130813862</v>
+        <v>1.246397079310445</v>
       </c>
       <c r="O5" s="5">
         <v>6</v>
       </c>
       <c r="P5" s="4">
-        <v>0.4014013387567917</v>
+        <v>0.3914275758809375</v>
       </c>
       <c r="Q5" s="4">
         <v>0.2764455077557083</v>
@@ -8589,7 +8589,7 @@
         <v>1</v>
       </c>
       <c r="N6" s="4">
-        <v>1.424126571414789</v>
+        <v>1.355060420788359</v>
       </c>
       <c r="O6" s="5">
         <v>6</v>
@@ -8828,16 +8828,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.1296480868631594</v>
+        <v>0.09251128923278779</v>
       </c>
       <c r="O3" s="5">
         <v>6</v>
       </c>
       <c r="P3" s="4">
-        <v>0.299383826329591</v>
+        <v>0.2867151222762077</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.181094321118276</v>
+        <v>0.1765816482572221</v>
       </c>
       <c r="R3" s="5">
         <v>6</v>
@@ -8887,7 +8887,7 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.245530641908394</v>
+        <v>0.2470584697493653</v>
       </c>
       <c r="O4" s="5">
         <v>8</v>
@@ -8946,16 +8946,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.7422507120651293</v>
+        <v>0.7641938602974921</v>
       </c>
       <c r="O5" s="5">
         <v>7</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1882895261806924</v>
+        <v>0.1790166607410816</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1594760937505901</v>
+        <v>0.1520132687099438</v>
       </c>
       <c r="R5" s="5">
         <v>7</v>
@@ -9005,22 +9005,22 @@
         <v>1</v>
       </c>
       <c r="N6" s="4">
-        <v>2.699110694473406</v>
+        <v>0.9722983417415335</v>
       </c>
       <c r="O6" s="5">
         <v>5</v>
       </c>
       <c r="P6" s="4">
-        <v>2.36196978431513</v>
+        <v>1.803431808842354</v>
       </c>
       <c r="Q6" s="4">
-        <v>1.46151626795955</v>
+        <v>0.3900201739989434</v>
       </c>
       <c r="R6" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S6" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:19" ht="25" customHeight="1">
@@ -9064,16 +9064,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.312290228982436</v>
+        <v>-0.3237556373428618</v>
       </c>
       <c r="O7" s="5">
         <v>5</v>
       </c>
       <c r="P7" s="4">
-        <v>0.09740583936886088</v>
+        <v>0.09247452592867871</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.09740583936886088</v>
+        <v>0.09247452592867871</v>
       </c>
       <c r="R7" s="5">
         <v>5</v>
@@ -9360,7 +9360,7 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.6683149253870521</v>
+        <v>0.6797184420611562</v>
       </c>
       <c r="O5" s="5">
         <v>6</v>
@@ -9369,7 +9369,7 @@
         <v>0.44413851224025</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.4068160288156563</v>
+        <v>0.4068160288156562</v>
       </c>
       <c r="R5" s="5">
         <v>6</v>
@@ -9884,16 +9884,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.2732386962370747</v>
+        <v>-0.2785578700335547</v>
       </c>
       <c r="O7" s="5">
         <v>5</v>
       </c>
       <c r="P7" s="4">
-        <v>0.162592328092926</v>
+        <v>0.16152849333363</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.162592328092926</v>
+        <v>0.16152849333363</v>
       </c>
       <c r="R7" s="5">
         <v>5</v>
